--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -1,19 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74C27BE-7312-4C26-BAC3-DEABC6EF9CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
+    <sheet name="Reputation, Society" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -22,223 +15,114 @@
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
-  <si>
-    <t>KPI by FTE</t>
-  </si>
-  <si>
-    <t>Recognition and Reputation</t>
-  </si>
-  <si>
-    <t>Society Impact &amp; Inclusion</t>
-  </si>
-  <si>
-    <t>Number of collaborations with ARIs</t>
-  </si>
-  <si>
-    <t>Number of active collaborations with scaling partners</t>
-  </si>
-  <si>
-    <t>Number of awards granted to IITA staff/project teams</t>
-  </si>
-  <si>
-    <t>Number of invitations to IITA staff to give seminars, as guest speakers etc.</t>
-  </si>
-  <si>
-    <t>Number of direct engagements  with senior policymakers to provide strategic advice, influence reforms, or shape national strategies.</t>
-  </si>
-  <si>
-    <t>Approved proposals with gender/youth/social inclusion components (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>Approved proposals with inclusion of adaptation/ mitigation activities  (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>Approved proposals with inclusion of nutrition and health activities (target is 25% of total approved proposals)</t>
-  </si>
-  <si>
-    <t>GI</t>
-  </si>
-  <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Breeding</t>
-  </si>
-  <si>
-    <t>Genebanks</t>
-  </si>
-  <si>
-    <t>Seed System</t>
-  </si>
-  <si>
-    <t>RAFS</t>
-  </si>
-  <si>
-    <t>Plant Health</t>
-  </si>
-  <si>
-    <t>Farming Systems Agronomy</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>Mechanization</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>FIAS</t>
-  </si>
-  <si>
-    <t>GeYSI</t>
-  </si>
-  <si>
-    <t>RCA</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>VCMA</t>
-  </si>
-  <si>
-    <t>per Program Target (target/13)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0070C0"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF00B0F0"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0070C0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -739,242 +623,407 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="92">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
@@ -1371,580 +1420,644 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D64F6B4-64C6-41A0-9F63-399977D02850}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AB21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" style="1" customWidth="1"/>
-    <col min="4" max="10" width="8.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" style="28" customWidth="1"/>
-    <col min="12" max="12" width="5.44140625" style="28" customWidth="1"/>
-    <col min="13" max="14" width="8.21875" style="3" customWidth="1"/>
+    <col width="3.21875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="25.33203125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="8.5546875" customWidth="1" style="1" min="4" max="10"/>
+    <col width="8.5546875" customWidth="1" style="74" min="11" max="11"/>
+    <col width="5.44140625" customWidth="1" style="74" min="12" max="12"/>
+    <col width="8.21875" customWidth="1" style="75" min="13" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1">
-      <c r="C1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="2"/>
+    <row r="1" ht="15" customHeight="1" thickBot="1">
+      <c r="C1" s="65" t="inlineStr">
+        <is>
+          <t>KPI by FTE</t>
+        </is>
+      </c>
+      <c r="D1" s="76" t="n"/>
+      <c r="E1" s="76" t="n"/>
+      <c r="F1" s="76" t="n"/>
+      <c r="G1" s="76" t="n"/>
+      <c r="H1" s="76" t="n"/>
+      <c r="I1" s="76" t="n"/>
+      <c r="J1" s="76" t="n"/>
+      <c r="K1" s="77" t="n"/>
+      <c r="L1" s="78" t="n"/>
     </row>
-    <row r="2" spans="2:14" s="8" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="72"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+    <row r="2" ht="25.95" customFormat="1" customHeight="1" s="8" thickBot="1">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="69" t="inlineStr">
+        <is>
+          <t>Recognition and Reputation</t>
+        </is>
+      </c>
+      <c r="E2" s="79" t="n"/>
+      <c r="F2" s="79" t="n"/>
+      <c r="G2" s="79" t="n"/>
+      <c r="H2" s="80" t="n"/>
+      <c r="I2" s="73" t="inlineStr">
+        <is>
+          <t>Society Impact &amp; Inclusion</t>
+        </is>
+      </c>
+      <c r="J2" s="76" t="n"/>
+      <c r="K2" s="81" t="n"/>
+      <c r="L2" s="82" t="n"/>
+      <c r="M2" s="83" t="n"/>
+      <c r="N2" s="83" t="n"/>
     </row>
-    <row r="3" spans="2:14" s="18" customFormat="1" ht="132" customHeight="1" thickBot="1">
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+    <row r="3" ht="132" customFormat="1" customHeight="1" s="18" thickBot="1">
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>ARIs collaborations</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Active collaborations with scaling partners</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Awards grated to IITA stafff</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Invitations to give seminars/talks</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>High level engagements</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Approved proposals with GeYSI components</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>Approved proposals with climate components</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>Approved proposals with nutrition and health components</t>
+        </is>
+      </c>
+      <c r="L3" s="78" t="n"/>
+      <c r="M3" s="84" t="n"/>
+      <c r="N3" s="84" t="n"/>
     </row>
-    <row r="4" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2.4285714285714284</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>13</v>
+    <row r="4" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>GI</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F4" s="22">
         <f>[1]Sheet1!$U$18</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="G4" s="23">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25">
-        <v>0</v>
-      </c>
-      <c r="J4" s="26">
-        <v>0</v>
-      </c>
-      <c r="K4" s="27">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
+        <v/>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="78" t="n"/>
+      <c r="M4" s="74" t="n"/>
+      <c r="N4" s="74" t="n"/>
     </row>
-    <row r="5" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="60"/>
-      <c r="C5" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="20">
+    <row r="5" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B5" s="85" t="n"/>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Breeding</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="22">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0.13043478260869565</v>
-      </c>
-      <c r="H5" s="24"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="H5" s="24" t="n"/>
       <c r="I5" s="31">
         <f>[1]Sheet1!$W$21</f>
-        <v>8.6956521739130432E-2</v>
+        <v/>
       </c>
       <c r="J5" s="32">
         <f>[1]Sheet1!$W$22</f>
-        <v>4.3478260869565216E-2</v>
+        <v/>
       </c>
       <c r="K5" s="24">
         <f>[1]Sheet1!$W$23</f>
-        <v>8.6956521739130432E-2</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
+        <v/>
+      </c>
+      <c r="L5" s="78" t="n"/>
+      <c r="M5" s="74" t="n"/>
+      <c r="N5" s="74" t="n"/>
     </row>
-    <row r="6" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="60"/>
-      <c r="C6" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="20">
+    <row r="6" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B6" s="85" t="n"/>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Genebanks</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n">
         <v>4.75</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="22">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23">
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="31">
-        <v>0</v>
-      </c>
-      <c r="J6" s="32">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="78" t="n"/>
+      <c r="M6" s="74" t="n"/>
+      <c r="N6" s="74" t="n"/>
     </row>
-    <row r="7" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="61"/>
-      <c r="C7" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="20">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0.93333333333333335</v>
+    <row r="7" ht="15.6" customFormat="1" customHeight="1" s="29" thickBot="1">
+      <c r="B7" s="86" t="n"/>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>Seed System</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.9333333333333333</v>
       </c>
       <c r="F7" s="22">
         <f>[1]Sheet1!$AA$18</f>
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0</v>
-      </c>
-      <c r="H7" s="24"/>
+        <v/>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24" t="n"/>
       <c r="I7" s="34">
         <f>[1]Sheet1!$AA$21</f>
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="J7" s="35">
         <f>[1]Sheet1!$AA$22</f>
-        <v>0.13333333333333333</v>
+        <v/>
       </c>
       <c r="K7" s="36">
         <f>[1]Sheet1!$AA$23</f>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
+        <v/>
+      </c>
+      <c r="L7" s="78" t="n"/>
+      <c r="M7" s="74" t="n"/>
+      <c r="N7" s="74" t="n"/>
     </row>
-    <row r="8" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="20">
+    <row r="8" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>RAFS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Plant Health</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="E8" s="21">
-        <v>8.3333333333333329E-2</v>
+      <c r="E8" s="21" t="n">
+        <v>0.08333333333333333</v>
       </c>
       <c r="F8" s="22">
         <f>[1]Sheet1!$AC$18</f>
-        <v>0.25</v>
-      </c>
-      <c r="G8" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H8" s="24"/>
+        <v/>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H8" s="24" t="n"/>
       <c r="I8" s="25">
         <f>[1]Sheet1!$AC$21</f>
-        <v>8.3333333333333329E-2</v>
+        <v/>
       </c>
       <c r="J8" s="26">
         <f>[1]Sheet1!$AC$22</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K8" s="27">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
+        <v/>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="78" t="n"/>
+      <c r="M8" s="74" t="n"/>
+      <c r="N8" s="74" t="n"/>
     </row>
-    <row r="9" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="60"/>
-      <c r="C9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="20">
+    <row r="9" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Farming Systems Agronomy</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="n">
         <v>2.15</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="F9" s="22">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23">
+      <c r="F9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="H9" s="24"/>
+      <c r="H9" s="24" t="n"/>
       <c r="I9" s="31">
         <f>[1]Sheet1!$AE$21</f>
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="J9" s="32">
         <f>[1]Sheet1!$AE$22</f>
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="K9" s="24">
         <f>[1]Sheet1!$AE$23</f>
-        <v>0.05</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
+        <v/>
+      </c>
+      <c r="L9" s="78" t="n"/>
+      <c r="M9" s="74" t="n"/>
+      <c r="N9" s="74" t="n"/>
     </row>
-    <row r="10" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="60"/>
-      <c r="C10" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F10" s="22">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24"/>
+    <row r="10" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>NRM</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="n"/>
       <c r="I10" s="31">
         <f>[1]Sheet1!$AG$21</f>
-        <v>0.5714285714285714</v>
+        <v/>
       </c>
       <c r="J10" s="32">
         <f>[1]Sheet1!$AG$22</f>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="K10" s="24">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
+        <v/>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="78" t="n"/>
+      <c r="M10" s="74" t="n"/>
+      <c r="N10" s="74" t="n"/>
     </row>
-    <row r="11" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="61"/>
-      <c r="C11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0</v>
-      </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="34">
-        <v>0</v>
-      </c>
-      <c r="J11" s="35">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
+    <row r="11" ht="15.6" customFormat="1" customHeight="1" s="29" thickBot="1">
+      <c r="B11" s="86" t="n"/>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>Mechanization</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="78" t="n"/>
+      <c r="M11" s="74" t="n"/>
+      <c r="N11" s="74" t="n"/>
     </row>
-    <row r="12" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="20">
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0</v>
-      </c>
-      <c r="F12" s="22">
-        <v>0</v>
-      </c>
-      <c r="G12" s="39">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="40">
-        <v>0</v>
-      </c>
-      <c r="J12" s="41">
-        <v>0</v>
-      </c>
-      <c r="K12" s="42">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
+    <row r="12" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>FIAS</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="78" t="n"/>
+      <c r="M12" s="74" t="n"/>
+      <c r="N12" s="74" t="n"/>
     </row>
-    <row r="13" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="63"/>
-      <c r="C13" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="22">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39">
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="43">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32">
-        <v>0</v>
-      </c>
-      <c r="K13" s="24">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
+    <row r="13" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>GeYSI</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="78" t="n"/>
+      <c r="M13" s="74" t="n"/>
+      <c r="N13" s="74" t="n"/>
     </row>
-    <row r="14" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="63"/>
-      <c r="C14" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="20">
+    <row r="14" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B14" s="85" t="n"/>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="21" t="n">
         <v>0.6</v>
       </c>
-      <c r="F14" s="22">
-        <v>0</v>
-      </c>
-      <c r="G14" s="39">
+      <c r="F14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="43">
-        <v>0</v>
-      </c>
-      <c r="J14" s="32">
-        <v>0</v>
-      </c>
-      <c r="K14" s="24">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="78" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="74" t="n"/>
     </row>
-    <row r="15" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="63"/>
-      <c r="C15" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="20">
+    <row r="15" ht="15.6" customFormat="1" customHeight="1" s="29">
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
         <v>1.75</v>
       </c>
-      <c r="E15" s="21">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22">
-        <v>0</v>
-      </c>
-      <c r="G15" s="39">
-        <v>0</v>
-      </c>
-      <c r="H15" s="24"/>
-      <c r="I15" s="43">
-        <v>0</v>
-      </c>
-      <c r="J15" s="32">
-        <v>0</v>
-      </c>
-      <c r="K15" s="24">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
+      <c r="E15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="78" t="n"/>
+      <c r="M15" s="74" t="n"/>
+      <c r="N15" s="74" t="n"/>
     </row>
-    <row r="16" spans="2:14" s="29" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="64"/>
-      <c r="C16" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="45">
-        <v>0</v>
-      </c>
-      <c r="E16" s="46">
+    <row r="16" ht="15.45" customFormat="1" customHeight="1" s="29" thickBot="1">
+      <c r="B16" s="88" t="n"/>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>VCMA</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="47">
         <f>[1]Sheet1!$AS$18</f>
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="48">
-        <v>0</v>
-      </c>
-      <c r="H16" s="36"/>
+        <v/>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="36" t="n"/>
       <c r="I16" s="49">
         <f>[1]Sheet1!$AS$21</f>
-        <v>0.1</v>
-      </c>
-      <c r="J16" s="35">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
+        <v/>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="78" t="n"/>
+      <c r="M16" s="74" t="n"/>
+      <c r="N16" s="74" t="n"/>
     </row>
-    <row r="17" spans="2:28" s="54" customFormat="1">
-      <c r="B17" s="51"/>
-      <c r="C17" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="55">
-        <v>0.22556390977443608</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0.18796992481203006</v>
-      </c>
-      <c r="F17" s="55">
-        <v>0.22556390977443608</v>
-      </c>
-      <c r="G17" s="55">
-        <v>0.22556390977443608</v>
-      </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="56">
-        <v>1.8796992481203006E-3</v>
-      </c>
-      <c r="J17" s="56">
-        <v>1.8796992481203006E-3</v>
-      </c>
-      <c r="K17" s="56">
-        <v>1.8796992481203006E-3</v>
-      </c>
-      <c r="L17" s="51"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="53"/>
-      <c r="V17" s="53"/>
-      <c r="W17" s="53"/>
-      <c r="X17" s="53"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="53"/>
-      <c r="AB17" s="53"/>
+    <row r="17" customFormat="1" s="54">
+      <c r="B17" s="51" t="n"/>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>per Program Target (target/13)</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="n">
+        <v>0.2255639097744361</v>
+      </c>
+      <c r="E17" s="89" t="n">
+        <v>0.1879699248120301</v>
+      </c>
+      <c r="F17" s="89" t="n">
+        <v>0.2255639097744361</v>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>0.2255639097744361</v>
+      </c>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="90" t="n">
+        <v>0.001879699248120301</v>
+      </c>
+      <c r="J17" s="90" t="n">
+        <v>0.001879699248120301</v>
+      </c>
+      <c r="K17" s="90" t="n">
+        <v>0.001879699248120301</v>
+      </c>
+      <c r="L17" s="51" t="n"/>
+      <c r="M17" s="91" t="n"/>
+      <c r="N17" s="91" t="n"/>
+      <c r="O17" s="91" t="n"/>
+      <c r="P17" s="91" t="n"/>
+      <c r="Q17" s="91" t="n"/>
+      <c r="R17" s="91" t="n"/>
+      <c r="S17" s="91" t="n"/>
+      <c r="T17" s="91" t="n"/>
+      <c r="U17" s="91" t="n"/>
+      <c r="V17" s="91" t="n"/>
+      <c r="W17" s="91" t="n"/>
+      <c r="X17" s="91" t="n"/>
+      <c r="Y17" s="91" t="n"/>
+      <c r="Z17" s="91" t="n"/>
+      <c r="AA17" s="91" t="n"/>
+      <c r="AB17" s="91" t="n"/>
     </row>
-    <row r="19" spans="2:28" hidden="1">
-      <c r="B19" s="57"/>
-      <c r="D19" s="58"/>
+    <row r="18"/>
+    <row r="19" hidden="1">
+      <c r="B19" s="57" t="n"/>
+      <c r="D19" s="58" t="n"/>
     </row>
-    <row r="20" spans="2:28" hidden="1">
-      <c r="B20" s="57"/>
-      <c r="D20" s="50"/>
+    <row r="20" hidden="1">
+      <c r="B20" s="57" t="n"/>
+      <c r="D20" s="50" t="n"/>
     </row>
-    <row r="21" spans="2:28" hidden="1">
-      <c r="B21" s="57"/>
-      <c r="D21" s="57"/>
+    <row r="21" hidden="1">
+      <c r="B21" s="57" t="n"/>
+      <c r="D21" s="57" t="n"/>
     </row>
-    <row r="22" spans="2:28" hidden="1"/>
-    <row r="23" spans="2:28" hidden="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="D2:H2"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
     <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="38">
@@ -2031,12 +2144,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="88"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -1,12 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1FBC159A-5CF3-401E-9AA6-D9C1E3BCFE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Reputation, Society" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -15,114 +22,221 @@
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+  <si>
+    <t>KPI by FTE</t>
+  </si>
+  <si>
+    <t>Recognition and Reputation</t>
+  </si>
+  <si>
+    <t>Society Impact &amp; Inclusion</t>
+  </si>
+  <si>
+    <t>ARIs collaborations</t>
+  </si>
+  <si>
+    <t>Active collaborations with scaling partners</t>
+  </si>
+  <si>
+    <t>Awards grated to IITA stafff</t>
+  </si>
+  <si>
+    <t>Invitations to give seminars/talks</t>
+  </si>
+  <si>
+    <t>High level engagements</t>
+  </si>
+  <si>
+    <t>Approved proposals with GeYSI components</t>
+  </si>
+  <si>
+    <t>Approved proposals with climate components</t>
+  </si>
+  <si>
+    <t>Approved proposals with nutrition and health components</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>FIAS</t>
+  </si>
+  <si>
+    <t>GeYSI</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>VCMA</t>
+  </si>
+  <si>
+    <t>per Program Target (target/13)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -149,19 +263,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -231,21 +332,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -382,52 +468,26 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
-        <color rgb="FF00B050"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF00B050"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -499,17 +559,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -649,11 +698,15 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -664,373 +717,285 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="72">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="PR 1"/>
+      <sheetName val="PR 2"/>
+      <sheetName val="PR 3"/>
+      <sheetName val="PR 4"/>
+      <sheetName val="PR 5"/>
+      <sheetName val="PR 6"/>
+      <sheetName val="PR 7"/>
+      <sheetName val="PR 8"/>
+      <sheetName val="PR 9"/>
+      <sheetName val="PR 10"/>
+      <sheetName val="PR 11"/>
+      <sheetName val="PR 12"/>
+      <sheetName val="PR 13"/>
+      <sheetName val="PR 14"/>
+      <sheetName val="PR15"/>
+      <sheetName val="PR 16"/>
+      <sheetName val="PR 18"/>
+      <sheetName val="PR 19"/>
+      <sheetName val="PR20"/>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
+        <row r="4">
+          <cell r="G4">
+            <v>0.65217391304347827</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="4">
+          <cell r="G4">
+            <v>6.521739130434782E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="G5">
+            <v>0.25</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
         <row r="12">
           <cell r="I12">
             <v>1.4999999999999999E-2</v>
@@ -1048,54 +1013,6 @@
           </cell>
           <cell r="AS18">
             <v>0.1</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="W21">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-          <cell r="AA21">
-            <v>0.2</v>
-          </cell>
-          <cell r="AC21">
-            <v>8.3333333333333329E-2</v>
-          </cell>
-          <cell r="AE21">
-            <v>0.2</v>
-          </cell>
-          <cell r="AG21">
-            <v>0.5714285714285714</v>
-          </cell>
-          <cell r="AS21">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="W22">
-            <v>4.3478260869565216E-2</v>
-          </cell>
-          <cell r="AA22">
-            <v>0.13333333333333333</v>
-          </cell>
-          <cell r="AC22">
-            <v>8.3333333333333329E-2</v>
-          </cell>
-          <cell r="AE22">
-            <v>0.2</v>
-          </cell>
-          <cell r="AG22">
-            <v>0.7142857142857143</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="W23">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-          <cell r="AA23">
-            <v>6.6666666666666666E-2</v>
-          </cell>
-          <cell r="AE23">
-            <v>0.05</v>
           </cell>
         </row>
       </sheetData>
@@ -1420,644 +1337,566 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="B1:AB23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="3.21875" customWidth="1" style="1" min="2" max="2"/>
-    <col width="25.33203125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="8.5546875" customWidth="1" style="1" min="4" max="10"/>
-    <col width="8.5546875" customWidth="1" style="74" min="11" max="11"/>
-    <col width="5.44140625" customWidth="1" style="74" min="12" max="12"/>
-    <col width="8.21875" customWidth="1" style="75" min="13" max="14"/>
+    <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="1" customWidth="1"/>
+    <col min="4" max="10" width="8.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="28" customWidth="1"/>
+    <col min="12" max="12" width="5.44140625" style="28" customWidth="1"/>
+    <col min="13" max="14" width="8.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" thickBot="1">
-      <c r="C1" s="65" t="inlineStr">
-        <is>
-          <t>KPI by FTE</t>
-        </is>
-      </c>
-      <c r="D1" s="76" t="n"/>
-      <c r="E1" s="76" t="n"/>
-      <c r="F1" s="76" t="n"/>
-      <c r="G1" s="76" t="n"/>
-      <c r="H1" s="76" t="n"/>
-      <c r="I1" s="76" t="n"/>
-      <c r="J1" s="76" t="n"/>
-      <c r="K1" s="77" t="n"/>
-      <c r="L1" s="78" t="n"/>
+    <row r="1" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="2"/>
     </row>
-    <row r="2" ht="25.95" customFormat="1" customHeight="1" s="8" thickBot="1">
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="69" t="inlineStr">
-        <is>
-          <t>Recognition and Reputation</t>
-        </is>
-      </c>
-      <c r="E2" s="79" t="n"/>
-      <c r="F2" s="79" t="n"/>
-      <c r="G2" s="79" t="n"/>
-      <c r="H2" s="80" t="n"/>
-      <c r="I2" s="73" t="inlineStr">
-        <is>
-          <t>Society Impact &amp; Inclusion</t>
-        </is>
-      </c>
-      <c r="J2" s="76" t="n"/>
-      <c r="K2" s="81" t="n"/>
-      <c r="L2" s="82" t="n"/>
-      <c r="M2" s="83" t="n"/>
-      <c r="N2" s="83" t="n"/>
+    <row r="2" spans="2:14" s="8" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="60"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
-    <row r="3" ht="132" customFormat="1" customHeight="1" s="18" thickBot="1">
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>ARIs collaborations</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Active collaborations with scaling partners</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>Awards grated to IITA stafff</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Invitations to give seminars/talks</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>High level engagements</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>Approved proposals with GeYSI components</t>
-        </is>
-      </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>Approved proposals with climate components</t>
-        </is>
-      </c>
-      <c r="K3" s="16" t="inlineStr">
-        <is>
-          <t>Approved proposals with nutrition and health components</t>
-        </is>
-      </c>
-      <c r="L3" s="78" t="n"/>
-      <c r="M3" s="84" t="n"/>
-      <c r="N3" s="84" t="n"/>
+    <row r="3" spans="2:14" s="18" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
     </row>
-    <row r="4" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B4" s="59" t="inlineStr">
-        <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>Biotech</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n">
-        <v>2.428571428571428</v>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="4" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="20">
+        <v>2.4285714285714279</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="F4" s="22">
         <f>[1]Sheet1!$U$18</f>
-        <v/>
-      </c>
-      <c r="G4" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24" t="n"/>
-      <c r="I4" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="78" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="74" t="n"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25">
+        <v>0</v>
+      </c>
+      <c r="J4" s="26">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
     </row>
-    <row r="5" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B5" s="85" t="n"/>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>Breeding</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="n">
+    <row r="5" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="65"/>
+      <c r="C5" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="20">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0.1304347826086956</v>
-      </c>
-      <c r="H5" s="24" t="n"/>
+      <c r="E5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="22">
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0.13043478260869559</v>
+      </c>
+      <c r="H5" s="24"/>
       <c r="I5" s="31">
-        <f>[1]Sheet1!$W$21</f>
-        <v/>
+        <v>0.09</v>
       </c>
       <c r="J5" s="32">
-        <f>[1]Sheet1!$W$22</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="K5" s="24">
-        <f>[1]Sheet1!$W$23</f>
-        <v/>
-      </c>
-      <c r="L5" s="78" t="n"/>
-      <c r="M5" s="74" t="n"/>
-      <c r="N5" s="74" t="n"/>
+        <v>0.09</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
     </row>
-    <row r="6" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B6" s="85" t="n"/>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>Genebanks</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="n">
+    <row r="6" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="65"/>
+      <c r="C6" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="20">
         <v>4.75</v>
       </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="n">
+      <c r="E6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="22">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23">
         <v>0.25</v>
       </c>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="78" t="n"/>
-      <c r="M6" s="74" t="n"/>
-      <c r="N6" s="74" t="n"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="31">
+        <v>0</v>
+      </c>
+      <c r="J6" s="32">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
     </row>
-    <row r="7" ht="15.6" customFormat="1" customHeight="1" s="29" thickBot="1">
-      <c r="B7" s="86" t="n"/>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>Seed System</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>0.9333333333333333</v>
+    <row r="7" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="66"/>
+      <c r="C7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0.93333333333333335</v>
       </c>
       <c r="F7" s="22">
         <f>[1]Sheet1!$AA$18</f>
-        <v/>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="24" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24"/>
       <c r="I7" s="34">
-        <f>[1]Sheet1!$AA$21</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="J7" s="35">
-        <f>[1]Sheet1!$AA$22</f>
-        <v/>
+        <v>0.13</v>
       </c>
       <c r="K7" s="36">
-        <f>[1]Sheet1!$AA$23</f>
-        <v/>
-      </c>
-      <c r="L7" s="78" t="n"/>
-      <c r="M7" s="74" t="n"/>
-      <c r="N7" s="74" t="n"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
     </row>
-    <row r="8" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B8" s="59" t="inlineStr">
-        <is>
-          <t>RAFS</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Plant Health</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="n">
+    <row r="8" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="20">
         <v>1.5</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>0.08333333333333333</v>
+      <c r="E8" s="21">
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="F8" s="22">
         <f>[1]Sheet1!$AC$18</f>
-        <v/>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="H8" s="24" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H8" s="24"/>
       <c r="I8" s="25">
-        <f>[1]Sheet1!$AC$21</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="J8" s="26">
-        <f>[1]Sheet1!$AC$22</f>
-        <v/>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="78" t="n"/>
-      <c r="M8" s="74" t="n"/>
-      <c r="N8" s="74" t="n"/>
+        <v>0.08</v>
+      </c>
+      <c r="K8" s="27">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
     </row>
-    <row r="9" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B9" s="85" t="n"/>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>Farming Systems Agronomy</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="n">
+    <row r="9" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="65"/>
+      <c r="C9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="20">
         <v>2.15</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="21">
         <v>0.85</v>
       </c>
-      <c r="F9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23" t="n">
+      <c r="F9" s="22">
+        <v>0</v>
+      </c>
+      <c r="G9" s="23">
         <v>0.15</v>
       </c>
-      <c r="H9" s="24" t="n"/>
+      <c r="H9" s="24"/>
       <c r="I9" s="31">
-        <f>[1]Sheet1!$AE$21</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="J9" s="32">
-        <f>[1]Sheet1!$AE$22</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="K9" s="24">
-        <f>[1]Sheet1!$AE$23</f>
-        <v/>
-      </c>
-      <c r="L9" s="78" t="n"/>
-      <c r="M9" s="74" t="n"/>
-      <c r="N9" s="74" t="n"/>
+        <v>0.05</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
     </row>
-    <row r="10" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B10" s="85" t="n"/>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>NRM</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24" t="n"/>
+    <row r="10" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="65"/>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0.42857142857142849</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24"/>
       <c r="I10" s="31">
-        <f>[1]Sheet1!$AG$21</f>
-        <v/>
+        <v>0.56999999999999995</v>
       </c>
       <c r="J10" s="32">
-        <f>[1]Sheet1!$AG$22</f>
-        <v/>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="78" t="n"/>
-      <c r="M10" s="74" t="n"/>
-      <c r="N10" s="74" t="n"/>
+        <v>0.71</v>
+      </c>
+      <c r="K10" s="24">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
     </row>
-    <row r="11" ht="15.6" customFormat="1" customHeight="1" s="29" thickBot="1">
-      <c r="B11" s="86" t="n"/>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>Mechanization</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="78" t="n"/>
-      <c r="M11" s="74" t="n"/>
-      <c r="N11" s="74" t="n"/>
+    <row r="11" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="66"/>
+      <c r="C11" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="22">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24"/>
+      <c r="I11" s="34">
+        <v>0</v>
+      </c>
+      <c r="J11" s="35">
+        <v>0</v>
+      </c>
+      <c r="K11" s="36">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
     </row>
-    <row r="12" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B12" s="87" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>FIAS</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="78" t="n"/>
-      <c r="M12" s="74" t="n"/>
-      <c r="N12" s="74" t="n"/>
+    <row r="12" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="20">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="E12" s="21">
+        <v>0</v>
+      </c>
+      <c r="F12" s="22">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39">
+        <v>0</v>
+      </c>
+      <c r="H12" s="24"/>
+      <c r="I12" s="40">
+        <v>0</v>
+      </c>
+      <c r="J12" s="41">
+        <v>0</v>
+      </c>
+      <c r="K12" s="42">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
     </row>
-    <row r="13" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B13" s="85" t="n"/>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>GeYSI</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="78" t="n"/>
-      <c r="M13" s="74" t="n"/>
-      <c r="N13" s="74" t="n"/>
+    <row r="13" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="65"/>
+      <c r="C13" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="20">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21">
+        <v>0</v>
+      </c>
+      <c r="F13" s="22">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="H13" s="24"/>
+      <c r="I13" s="43">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
     </row>
-    <row r="14" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B14" s="85" t="n"/>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n">
+    <row r="14" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="65"/>
+      <c r="C14" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="20">
         <v>1.2</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="21">
         <v>0.6</v>
       </c>
-      <c r="F14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="39" t="n">
+      <c r="F14" s="22">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39">
         <v>0.6</v>
       </c>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="78" t="n"/>
-      <c r="M14" s="74" t="n"/>
-      <c r="N14" s="74" t="n"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="43">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32">
+        <v>0</v>
+      </c>
+      <c r="K14" s="24">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
     </row>
-    <row r="15" ht="15.6" customFormat="1" customHeight="1" s="29">
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>Nutrition</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
+    <row r="15" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="65"/>
+      <c r="C15" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="20">
         <v>1.75</v>
       </c>
-      <c r="E15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="24" t="n"/>
-      <c r="I15" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="78" t="n"/>
-      <c r="M15" s="74" t="n"/>
-      <c r="N15" s="74" t="n"/>
+      <c r="E15" s="21">
+        <v>0</v>
+      </c>
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="39">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="43">
+        <v>0</v>
+      </c>
+      <c r="J15" s="32">
+        <v>0</v>
+      </c>
+      <c r="K15" s="24">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
     </row>
-    <row r="16" ht="15.45" customFormat="1" customHeight="1" s="29" thickBot="1">
-      <c r="B16" s="88" t="n"/>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>VCMA</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="46" t="n">
+    <row r="16" spans="2:14" s="29" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="71"/>
+      <c r="C16" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="45">
+        <v>0</v>
+      </c>
+      <c r="E16" s="46">
         <v>0</v>
       </c>
       <c r="F16" s="47">
         <f>[1]Sheet1!$AS$18</f>
-        <v/>
-      </c>
-      <c r="G16" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="36" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="48">
+        <v>0</v>
+      </c>
+      <c r="H16" s="36"/>
       <c r="I16" s="49">
-        <f>[1]Sheet1!$AS$21</f>
-        <v/>
-      </c>
-      <c r="J16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="78" t="n"/>
-      <c r="M16" s="74" t="n"/>
-      <c r="N16" s="74" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="J16" s="35">
+        <v>0</v>
+      </c>
+      <c r="K16" s="36">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
     </row>
-    <row r="17" customFormat="1" s="54">
-      <c r="B17" s="51" t="n"/>
-      <c r="C17" s="52" t="inlineStr">
-        <is>
-          <t>per Program Target (target/13)</t>
-        </is>
-      </c>
-      <c r="D17" s="89" t="n">
-        <v>0.2255639097744361</v>
-      </c>
-      <c r="E17" s="89" t="n">
-        <v>0.1879699248120301</v>
-      </c>
-      <c r="F17" s="89" t="n">
-        <v>0.2255639097744361</v>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.2255639097744361</v>
-      </c>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="90" t="n">
-        <v>0.001879699248120301</v>
-      </c>
-      <c r="J17" s="90" t="n">
-        <v>0.001879699248120301</v>
-      </c>
-      <c r="K17" s="90" t="n">
-        <v>0.001879699248120301</v>
-      </c>
-      <c r="L17" s="51" t="n"/>
-      <c r="M17" s="91" t="n"/>
-      <c r="N17" s="91" t="n"/>
-      <c r="O17" s="91" t="n"/>
-      <c r="P17" s="91" t="n"/>
-      <c r="Q17" s="91" t="n"/>
-      <c r="R17" s="91" t="n"/>
-      <c r="S17" s="91" t="n"/>
-      <c r="T17" s="91" t="n"/>
-      <c r="U17" s="91" t="n"/>
-      <c r="V17" s="91" t="n"/>
-      <c r="W17" s="91" t="n"/>
-      <c r="X17" s="91" t="n"/>
-      <c r="Y17" s="91" t="n"/>
-      <c r="Z17" s="91" t="n"/>
-      <c r="AA17" s="91" t="n"/>
-      <c r="AB17" s="91" t="n"/>
+    <row r="17" spans="2:28" s="54" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="51"/>
+      <c r="C17" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="55">
+        <v>0.22556390977443611</v>
+      </c>
+      <c r="E17" s="55">
+        <v>0.18796992481203009</v>
+      </c>
+      <c r="F17" s="55">
+        <v>0.22556390977443611</v>
+      </c>
+      <c r="G17" s="55">
+        <v>0.22556390977443611</v>
+      </c>
+      <c r="H17" s="52"/>
+      <c r="I17" s="56">
+        <v>1.8796992481203011E-3</v>
+      </c>
+      <c r="J17" s="56">
+        <v>1.8796992481203011E-3</v>
+      </c>
+      <c r="K17" s="56">
+        <v>1.8796992481203011E-3</v>
+      </c>
+      <c r="L17" s="51"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="Z17" s="53"/>
+      <c r="AA17" s="53"/>
+      <c r="AB17" s="53"/>
     </row>
-    <row r="18"/>
-    <row r="19" hidden="1">
-      <c r="B19" s="57" t="n"/>
-      <c r="D19" s="58" t="n"/>
+    <row r="19" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="57"/>
+      <c r="D19" s="58"/>
     </row>
-    <row r="20" hidden="1">
-      <c r="B20" s="57" t="n"/>
-      <c r="D20" s="50" t="n"/>
+    <row r="20" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="57"/>
+      <c r="D20" s="50"/>
     </row>
-    <row r="21" hidden="1">
-      <c r="B21" s="57" t="n"/>
-      <c r="D21" s="57" t="n"/>
+    <row r="21" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="57"/>
+      <c r="D21" s="57"/>
     </row>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
+    <row r="22" spans="2:28" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:28" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B12:B16"/>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B12:B16"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="38">
@@ -2144,6 +1983,12 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="88"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1FBC159A-5CF3-401E-9AA6-D9C1E3BCFE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842C1B9F-BB96-4072-8DCF-FC8F331343A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,13 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -52,94 +54,98 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>ARIs collaborations</t>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>per Program Target (target/13)</t>
+  </si>
+  <si>
+    <t>Collaboration with Agriculture Research Institutions</t>
   </si>
   <si>
     <t>Active collaborations with scaling partners</t>
   </si>
   <si>
-    <t>Awards grated to IITA stafff</t>
-  </si>
-  <si>
-    <t>Invitations to give seminars/talks</t>
+    <t>Awards granted to IITA staff or project teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Invitations for presentations or seminars</t>
   </si>
   <si>
     <t>High level engagements</t>
   </si>
   <si>
-    <t>Approved proposals with GeYSI components</t>
+    <t xml:space="preserve"> Approved proposals with GeYSI components</t>
   </si>
   <si>
     <t>Approved proposals with climate components</t>
   </si>
   <si>
-    <t>Approved proposals with nutrition and health components</t>
-  </si>
-  <si>
-    <t>GI</t>
-  </si>
-  <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Breeding</t>
-  </si>
-  <si>
-    <t>Genebanks</t>
-  </si>
-  <si>
-    <t>Seed System</t>
-  </si>
-  <si>
-    <t>RAFS</t>
-  </si>
-  <si>
-    <t>Plant Health</t>
-  </si>
-  <si>
-    <t>Farming Systems Agronomy</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>Mechanization</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>FIAS</t>
-  </si>
-  <si>
-    <t>GeYSI</t>
-  </si>
-  <si>
-    <t>RCA</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>VCMA</t>
-  </si>
-  <si>
-    <t>per Program Target (target/13)</t>
+    <t>Approved proposals with nutrition ad health components</t>
+  </si>
+  <si>
+    <t>FTE</t>
+  </si>
+  <si>
+    <t>Natural Resource Management</t>
+  </si>
+  <si>
+    <t>Foresight &amp; Impact Assessment</t>
+  </si>
+  <si>
+    <t>Gender, Youth &amp; Social Inclusion</t>
+  </si>
+  <si>
+    <t>Reslience &amp; Climate Adaptation</t>
+  </si>
+  <si>
+    <t>Nutrition and Health</t>
+  </si>
+  <si>
+    <t>Value Chain Markets and Agribusiness</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,26 +162,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -208,21 +194,28 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,8 +228,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="37">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -263,6 +262,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -332,6 +344,21 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -468,6 +495,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF00B050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -488,6 +528,19 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF00B050"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -559,6 +612,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -676,11 +740,129 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -697,7 +879,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -705,19 +889,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -725,192 +896,292 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -933,69 +1204,16 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="PR 1"/>
-      <sheetName val="PR 2"/>
-      <sheetName val="PR 3"/>
-      <sheetName val="PR 4"/>
-      <sheetName val="PR 5"/>
-      <sheetName val="PR 6"/>
-      <sheetName val="PR 7"/>
-      <sheetName val="PR 8"/>
-      <sheetName val="PR 9"/>
-      <sheetName val="PR 10"/>
-      <sheetName val="PR 11"/>
-      <sheetName val="PR 12"/>
-      <sheetName val="PR 13"/>
-      <sheetName val="PR 14"/>
-      <sheetName val="PR15"/>
-      <sheetName val="PR 16"/>
-      <sheetName val="PR 18"/>
-      <sheetName val="PR 19"/>
-      <sheetName val="PR20"/>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
-        <row r="4">
-          <cell r="G4">
-            <v>0.65217391304347827</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="4">
-          <cell r="G4">
-            <v>6.521739130434782E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="5">
-          <cell r="G5">
-            <v>0.25</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="1">
         <row r="12">
           <cell r="I12">
             <v>1.4999999999999999E-2</v>
@@ -1013,6 +1231,54 @@
           </cell>
           <cell r="AS18">
             <v>0.1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="W21">
+            <v>8.6956521739130432E-2</v>
+          </cell>
+          <cell r="AA21">
+            <v>0.2</v>
+          </cell>
+          <cell r="AC21">
+            <v>8.3333333333333329E-2</v>
+          </cell>
+          <cell r="AE21">
+            <v>0.2</v>
+          </cell>
+          <cell r="AG21">
+            <v>0.5714285714285714</v>
+          </cell>
+          <cell r="AS21">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="W22">
+            <v>4.3478260869565216E-2</v>
+          </cell>
+          <cell r="AA22">
+            <v>0.13333333333333333</v>
+          </cell>
+          <cell r="AC22">
+            <v>8.3333333333333329E-2</v>
+          </cell>
+          <cell r="AE22">
+            <v>0.2</v>
+          </cell>
+          <cell r="AG22">
+            <v>0.7142857142857143</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="W23">
+            <v>8.6956521739130432E-2</v>
+          </cell>
+          <cell r="AA23">
+            <v>6.6666666666666666E-2</v>
+          </cell>
+          <cell r="AE23">
+            <v>0.05</v>
           </cell>
         </row>
       </sheetData>
@@ -1337,581 +1603,629 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D64F6B4-64C6-41A0-9F63-399977D02850}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:AC23"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" style="1" customWidth="1"/>
-    <col min="4" max="10" width="8.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" style="28" customWidth="1"/>
-    <col min="12" max="12" width="5.44140625" style="28" customWidth="1"/>
-    <col min="13" max="14" width="8.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="85" customWidth="1"/>
+    <col min="5" max="11" width="8.5546875" style="52" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="53" customWidth="1"/>
+    <col min="13" max="13" width="5.44140625" style="8" customWidth="1"/>
+    <col min="14" max="15" width="8.21875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="2"/>
+    <row r="1" spans="2:15" s="20" customFormat="1" ht="15" thickBot="1">
+      <c r="B1" s="17"/>
+      <c r="C1" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
-    <row r="2" spans="2:14" s="8" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="67" t="s">
+    <row r="2" spans="2:15" s="24" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
+      <c r="B2" s="21"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="62" t="s">
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="60"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
     </row>
-    <row r="3" spans="2:14" s="18" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+    <row r="3" spans="2:15" s="6" customFormat="1" ht="132" customHeight="1" thickBot="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B4" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="D4" s="78">
+        <v>7</v>
+      </c>
+      <c r="E4" s="26">
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-    </row>
-    <row r="4" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2.4285714285714279</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="22">
+      <c r="G4" s="28">
         <f>[1]Sheet1!$U$18</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="G4" s="23">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25">
-        <v>0</v>
-      </c>
-      <c r="J4" s="26">
-        <v>0</v>
-      </c>
-      <c r="K4" s="27">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
+      <c r="H4" s="29">
+        <v>0</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="62">
+        <v>0</v>
+      </c>
+      <c r="K4" s="63">
+        <v>0</v>
+      </c>
+      <c r="L4" s="64">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="20">
+    <row r="5" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B5" s="87"/>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="79">
+        <v>23</v>
+      </c>
+      <c r="E5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="22">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0.13043478260869559</v>
-      </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="31">
-        <v>0.09</v>
-      </c>
-      <c r="J5" s="32">
-        <v>0.04</v>
-      </c>
-      <c r="K5" s="24">
-        <v>0.09</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
+      <c r="F5" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="33">
+        <v>0</v>
+      </c>
+      <c r="H5" s="34">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="65">
+        <f>[1]Sheet1!$W$21</f>
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="K5" s="66">
+        <f>[1]Sheet1!$W$22</f>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="L5" s="67">
+        <f>[1]Sheet1!$W$23</f>
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="30" t="s">
+    <row r="6" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B6" s="87"/>
+      <c r="C6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="79">
+        <v>4</v>
+      </c>
+      <c r="E6" s="31">
+        <v>4.75</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="33">
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="65">
+        <v>0</v>
+      </c>
+      <c r="K6" s="66">
+        <v>0</v>
+      </c>
+      <c r="L6" s="67">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B7" s="88"/>
+      <c r="C7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="80">
         <v>15</v>
       </c>
-      <c r="D6" s="20">
-        <v>4.75</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="22">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.25</v>
-      </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="31">
-        <v>0</v>
-      </c>
-      <c r="J6" s="32">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-    </row>
-    <row r="7" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66"/>
-      <c r="C7" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="20">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="E7" s="36">
+        <v>0</v>
+      </c>
+      <c r="F7" s="37">
         <v>0.93333333333333335</v>
       </c>
-      <c r="F7" s="22">
+      <c r="G7" s="38">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="G7" s="23">
-        <v>0</v>
-      </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="34">
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+      <c r="I7" s="40"/>
+      <c r="J7" s="68">
+        <f>[1]Sheet1!$AA$21</f>
         <v>0.2</v>
       </c>
-      <c r="J7" s="35">
-        <v>0.13</v>
-      </c>
-      <c r="K7" s="36">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
+      <c r="K7" s="69">
+        <f>[1]Sheet1!$AA$22</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="L7" s="70">
+        <f>[1]Sheet1!$AA$23</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="20">
+    <row r="8" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B8" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="78">
+        <v>12</v>
+      </c>
+      <c r="E8" s="26">
         <v>1.5</v>
       </c>
-      <c r="E8" s="21">
+      <c r="F8" s="27">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F8" s="22">
+      <c r="G8" s="28">
         <f>[1]Sheet1!$AC$18</f>
         <v>0.25</v>
       </c>
-      <c r="G8" s="23">
+      <c r="H8" s="29">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25">
-        <v>0.08</v>
-      </c>
-      <c r="J8" s="26">
-        <v>0.08</v>
-      </c>
-      <c r="K8" s="27">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="62">
+        <f>[1]Sheet1!$AC$21</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K8" s="63">
+        <f>[1]Sheet1!$AC$22</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="L8" s="64">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="65"/>
-      <c r="C9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="20">
+    <row r="9" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B9" s="87"/>
+      <c r="C9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="79">
+        <v>20</v>
+      </c>
+      <c r="E9" s="31">
         <v>2.15</v>
       </c>
-      <c r="E9" s="21">
+      <c r="F9" s="32">
         <v>0.85</v>
       </c>
-      <c r="F9" s="22">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23">
+      <c r="G9" s="33">
+        <v>0</v>
+      </c>
+      <c r="H9" s="34">
         <v>0.15</v>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="31">
+      <c r="I9" s="35"/>
+      <c r="J9" s="65">
+        <f>[1]Sheet1!$AE$21</f>
         <v>0.2</v>
       </c>
-      <c r="J9" s="32">
+      <c r="K9" s="66">
+        <f>[1]Sheet1!$AE$22</f>
         <v>0.2</v>
       </c>
-      <c r="K9" s="24">
+      <c r="L9" s="67">
+        <f>[1]Sheet1!$AE$23</f>
         <v>0.05</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="65"/>
-      <c r="C10" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.42857142857142849</v>
-      </c>
-      <c r="F10" s="22">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0</v>
-      </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="31">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J10" s="32">
-        <v>0.71</v>
-      </c>
-      <c r="K10" s="24">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
+    <row r="10" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B10" s="87"/>
+      <c r="C10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="79">
+        <v>7</v>
+      </c>
+      <c r="E10" s="31">
+        <v>0</v>
+      </c>
+      <c r="F10" s="32">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="G10" s="33">
+        <v>0</v>
+      </c>
+      <c r="H10" s="34">
+        <v>0</v>
+      </c>
+      <c r="I10" s="35"/>
+      <c r="J10" s="65">
+        <f>[1]Sheet1!$AG$21</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K10" s="66">
+        <f>[1]Sheet1!$AG$22</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="L10" s="67">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="66"/>
-      <c r="C11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0</v>
-      </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="34">
-        <v>0</v>
-      </c>
-      <c r="J11" s="35">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
+    <row r="11" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B11" s="88"/>
+      <c r="C11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="80">
+        <v>4</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37">
+        <v>0</v>
+      </c>
+      <c r="G11" s="38">
+        <v>0</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+      <c r="I11" s="40"/>
+      <c r="J11" s="68">
+        <v>0</v>
+      </c>
+      <c r="K11" s="69">
+        <v>0</v>
+      </c>
+      <c r="L11" s="70">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="20">
+    <row r="12" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B12" s="89" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="81">
+        <v>11</v>
+      </c>
+      <c r="E12" s="41">
         <v>0.63636363636363635</v>
       </c>
-      <c r="E12" s="21">
-        <v>0</v>
-      </c>
-      <c r="F12" s="22">
-        <v>0</v>
-      </c>
-      <c r="G12" s="39">
-        <v>0</v>
-      </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="40">
-        <v>0</v>
-      </c>
-      <c r="J12" s="41">
-        <v>0</v>
-      </c>
-      <c r="K12" s="42">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
+      <c r="F12" s="42">
+        <v>0</v>
+      </c>
+      <c r="G12" s="43">
+        <v>0</v>
+      </c>
+      <c r="H12" s="44">
+        <v>0</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="71">
+        <v>0</v>
+      </c>
+      <c r="K12" s="72">
+        <v>0</v>
+      </c>
+      <c r="L12" s="73">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="65"/>
-      <c r="C13" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0</v>
-      </c>
-      <c r="F13" s="22">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39">
+    <row r="13" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B13" s="90"/>
+      <c r="C13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="82">
+        <v>11</v>
+      </c>
+      <c r="E13" s="31">
+        <v>0</v>
+      </c>
+      <c r="F13" s="32">
+        <v>0</v>
+      </c>
+      <c r="G13" s="33">
+        <v>0</v>
+      </c>
+      <c r="H13" s="46">
         <v>0.27272727272727271</v>
       </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="43">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32">
-        <v>0</v>
-      </c>
-      <c r="K13" s="24">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="74">
+        <v>0</v>
+      </c>
+      <c r="K13" s="66">
+        <v>0</v>
+      </c>
+      <c r="L13" s="67">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="65"/>
-      <c r="C14" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="20">
+    <row r="14" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B14" s="90"/>
+      <c r="C14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="82">
+        <v>5</v>
+      </c>
+      <c r="E14" s="31">
         <v>1.2</v>
       </c>
-      <c r="E14" s="21">
+      <c r="F14" s="32">
         <v>0.6</v>
       </c>
-      <c r="F14" s="22">
-        <v>0</v>
-      </c>
-      <c r="G14" s="39">
+      <c r="G14" s="33">
+        <v>0</v>
+      </c>
+      <c r="H14" s="46">
         <v>0.6</v>
       </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="43">
-        <v>0</v>
-      </c>
-      <c r="J14" s="32">
-        <v>0</v>
-      </c>
-      <c r="K14" s="24">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="74">
+        <v>0</v>
+      </c>
+      <c r="K14" s="66">
+        <v>0</v>
+      </c>
+      <c r="L14" s="67">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
-    <row r="15" spans="2:14" s="29" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="65"/>
-      <c r="C15" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="20">
+    <row r="15" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
+      <c r="B15" s="90"/>
+      <c r="C15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="82">
+        <v>4</v>
+      </c>
+      <c r="E15" s="31">
         <v>1.75</v>
       </c>
-      <c r="E15" s="21">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22">
-        <v>0</v>
-      </c>
-      <c r="G15" s="39">
-        <v>0</v>
-      </c>
-      <c r="H15" s="24"/>
-      <c r="I15" s="43">
-        <v>0</v>
-      </c>
-      <c r="J15" s="32">
-        <v>0</v>
-      </c>
-      <c r="K15" s="24">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
+      <c r="F15" s="32">
+        <v>0</v>
+      </c>
+      <c r="G15" s="33">
+        <v>0</v>
+      </c>
+      <c r="H15" s="46">
+        <v>0</v>
+      </c>
+      <c r="I15" s="35"/>
+      <c r="J15" s="74">
+        <v>0</v>
+      </c>
+      <c r="K15" s="66">
+        <v>0</v>
+      </c>
+      <c r="L15" s="67">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
-    <row r="16" spans="2:14" s="29" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="71"/>
-      <c r="C16" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="45">
-        <v>0</v>
-      </c>
-      <c r="E16" s="46">
-        <v>0</v>
-      </c>
-      <c r="F16" s="47">
+    <row r="16" spans="2:15" s="9" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
+      <c r="B16" s="91"/>
+      <c r="C16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="83">
+        <v>10</v>
+      </c>
+      <c r="E16" s="36">
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <v>0</v>
+      </c>
+      <c r="G16" s="47">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="G16" s="48">
-        <v>0</v>
-      </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="49">
+      <c r="H16" s="48">
+        <v>0</v>
+      </c>
+      <c r="I16" s="40"/>
+      <c r="J16" s="75">
+        <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="J16" s="35">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
+      <c r="K16" s="69">
+        <v>0</v>
+      </c>
+      <c r="L16" s="70">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
-    <row r="17" spans="2:28" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="51"/>
-      <c r="C17" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="55">
-        <v>0.22556390977443611</v>
-      </c>
-      <c r="E17" s="55">
-        <v>0.18796992481203009</v>
-      </c>
-      <c r="F17" s="55">
-        <v>0.22556390977443611</v>
-      </c>
-      <c r="G17" s="55">
-        <v>0.22556390977443611</v>
-      </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="56">
-        <v>1.8796992481203011E-3</v>
-      </c>
-      <c r="J17" s="56">
-        <v>1.8796992481203011E-3</v>
-      </c>
-      <c r="K17" s="56">
-        <v>1.8796992481203011E-3</v>
-      </c>
-      <c r="L17" s="51"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="53"/>
-      <c r="V17" s="53"/>
-      <c r="W17" s="53"/>
-      <c r="X17" s="53"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="53"/>
-      <c r="AB17" s="53"/>
+    <row r="17" spans="2:29">
+      <c r="B17" s="15"/>
+      <c r="C17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="84">
+        <v>133</v>
+      </c>
+      <c r="E17" s="49">
+        <v>0.22556390977443608</v>
+      </c>
+      <c r="F17" s="49">
+        <v>0.18796992481203006</v>
+      </c>
+      <c r="G17" s="49">
+        <v>0.22556390977443608</v>
+      </c>
+      <c r="H17" s="49">
+        <v>0.22556390977443608</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="61">
+        <v>1.8796992481203006E-3</v>
+      </c>
+      <c r="K17" s="61">
+        <v>1.8796992481203006E-3</v>
+      </c>
+      <c r="L17" s="61">
+        <v>1.8796992481203006E-3</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
     </row>
-    <row r="19" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="57"/>
-      <c r="D19" s="58"/>
+    <row r="19" spans="2:29" hidden="1">
+      <c r="E19" s="51"/>
     </row>
-    <row r="20" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="57"/>
-      <c r="D20" s="50"/>
+    <row r="20" spans="2:29" hidden="1"/>
+    <row r="21" spans="2:29" hidden="1">
+      <c r="E21" s="54"/>
     </row>
-    <row r="21" spans="2:28" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="57"/>
-      <c r="D21" s="57"/>
-    </row>
-    <row r="22" spans="2:28" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:28" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:29" hidden="1"/>
+    <row r="23" spans="2:29" hidden="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D16">
+  <conditionalFormatting sqref="E4:E16">
     <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$D$17/2"/>
-        <cfvo type="formula" val="$D$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -1923,7 +2237,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -1935,7 +2249,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -1946,12 +2260,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="42">
+  <conditionalFormatting sqref="H4:H16">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$I$17/2"/>
-        <cfvo type="formula" val="$I$17"/>
+        <cfvo type="formula" val="$H$17/2"/>
+        <cfvo type="formula" val="$H$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1959,7 +2273,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -1971,7 +2285,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
@@ -1982,8 +2296,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L4:L16">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$L$17/2"/>
+        <cfvo type="formula" val="$L$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="88" orientation="landscape"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842C1B9F-BB96-4072-8DCF-FC8F331343A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CABF64-DE01-47CF-BCF9-929CD1EAF1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$M$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -145,7 +145,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,22 +899,19 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -940,17 +937,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1608,613 +1597,560 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AC23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:X23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="41.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="85" customWidth="1"/>
-    <col min="5" max="11" width="8.5546875" style="52" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="53" customWidth="1"/>
-    <col min="13" max="13" width="5.44140625" style="8" customWidth="1"/>
-    <col min="14" max="15" width="8.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="78" customWidth="1"/>
+    <col min="5" max="11" width="8.5546875" style="45" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="20" customFormat="1" ht="15" thickBot="1">
-      <c r="B1" s="17"/>
-      <c r="C1" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+    <row r="1" spans="2:12" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="14"/>
+      <c r="C1" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
     </row>
-    <row r="2" spans="2:15" s="24" customFormat="1" ht="25.95" customHeight="1" thickBot="1">
-      <c r="B2" s="21"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="97" t="s">
+    <row r="2" spans="2:12" s="17" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="16"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="100" t="s">
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="100"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="94"/>
     </row>
-    <row r="3" spans="2:15" s="6" customFormat="1" ht="132" customHeight="1" thickBot="1">
-      <c r="B3" s="4"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="77" t="s">
+    <row r="3" spans="2:12" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="57" t="s">
+      <c r="F3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="K3" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="58" t="s">
+      <c r="L3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B4" s="86" t="s">
+    <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="71">
         <v>7</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="19">
         <v>2.4285714285714284</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="21">
         <f>[1]Sheet1!$U$18</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="29">
-        <v>0</v>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="62">
-        <v>0</v>
-      </c>
-      <c r="K4" s="63">
-        <v>0</v>
-      </c>
-      <c r="L4" s="64">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
+      <c r="H4" s="22">
+        <v>0</v>
+      </c>
+      <c r="I4" s="23"/>
+      <c r="J4" s="55">
+        <v>0</v>
+      </c>
+      <c r="K4" s="56">
+        <v>0</v>
+      </c>
+      <c r="L4" s="57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B5" s="87"/>
-      <c r="C5" s="10" t="s">
+    <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="80"/>
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="72">
         <v>23</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="24">
         <v>1</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="33">
-        <v>0</v>
-      </c>
-      <c r="H5" s="34">
+      <c r="G5" s="26">
+        <v>0</v>
+      </c>
+      <c r="H5" s="27">
         <v>0.13043478260869565</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="65">
+      <c r="I5" s="28"/>
+      <c r="J5" s="58">
         <f>[1]Sheet1!$W$21</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="59">
         <f>[1]Sheet1!$W$22</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="L5" s="67">
+      <c r="L5" s="60">
         <f>[1]Sheet1!$W$23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B6" s="87"/>
-      <c r="C6" s="10" t="s">
+    <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="80"/>
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="72">
         <v>4</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="24">
         <v>4.75</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="34">
+      <c r="G6" s="26">
+        <v>0</v>
+      </c>
+      <c r="H6" s="27">
         <v>0.25</v>
       </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="65">
-        <v>0</v>
-      </c>
-      <c r="K6" s="66">
-        <v>0</v>
-      </c>
-      <c r="L6" s="67">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="58">
+        <v>0</v>
+      </c>
+      <c r="K6" s="59">
+        <v>0</v>
+      </c>
+      <c r="L6" s="60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="88"/>
-      <c r="C7" s="11" t="s">
+    <row r="7" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="81"/>
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="73">
         <v>15</v>
       </c>
-      <c r="E7" s="36">
-        <v>0</v>
-      </c>
-      <c r="F7" s="37">
+      <c r="E7" s="29">
+        <v>0</v>
+      </c>
+      <c r="F7" s="30">
         <v>0.93333333333333335</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="31">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="H7" s="39">
-        <v>0</v>
-      </c>
-      <c r="I7" s="40"/>
-      <c r="J7" s="68">
+      <c r="H7" s="32">
+        <v>0</v>
+      </c>
+      <c r="I7" s="33"/>
+      <c r="J7" s="61">
         <f>[1]Sheet1!$AA$21</f>
         <v>0.2</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="62">
         <f>[1]Sheet1!$AA$22</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="63">
         <f>[1]Sheet1!$AA$23</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B8" s="86" t="s">
+    <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="78">
+      <c r="D8" s="71">
         <v>12</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="19">
         <v>1.5</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="20">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="21">
         <f>[1]Sheet1!$AC$18</f>
         <v>0.25</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="22">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="62">
+      <c r="I8" s="23"/>
+      <c r="J8" s="55">
         <f>[1]Sheet1!$AC$21</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K8" s="63">
+      <c r="K8" s="56">
         <f>[1]Sheet1!$AC$22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L8" s="64">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="L8" s="57">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B9" s="87"/>
-      <c r="C9" s="10" t="s">
+    <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="80"/>
+      <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="72">
         <v>20</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="24">
         <v>2.15</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="25">
         <v>0.85</v>
       </c>
-      <c r="G9" s="33">
-        <v>0</v>
-      </c>
-      <c r="H9" s="34">
+      <c r="G9" s="26">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27">
         <v>0.15</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="65">
+      <c r="I9" s="28"/>
+      <c r="J9" s="58">
         <f>[1]Sheet1!$AE$21</f>
         <v>0.2</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="59">
         <f>[1]Sheet1!$AE$22</f>
         <v>0.2</v>
       </c>
-      <c r="L9" s="67">
+      <c r="L9" s="60">
         <f>[1]Sheet1!$AE$23</f>
         <v>0.05</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B10" s="87"/>
-      <c r="C10" s="10" t="s">
+    <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="80"/>
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="72">
         <v>7</v>
       </c>
-      <c r="E10" s="31">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="E10" s="24">
+        <v>0</v>
+      </c>
+      <c r="F10" s="25">
         <v>0.42857142857142855</v>
       </c>
-      <c r="G10" s="33">
-        <v>0</v>
-      </c>
-      <c r="H10" s="34">
-        <v>0</v>
-      </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="65">
+      <c r="G10" s="26">
+        <v>0</v>
+      </c>
+      <c r="H10" s="27">
+        <v>0</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="J10" s="58">
         <f>[1]Sheet1!$AG$21</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="59">
         <f>[1]Sheet1!$AG$22</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="L10" s="67">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
+      <c r="L10" s="60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="88"/>
-      <c r="C11" s="11" t="s">
+    <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="81"/>
+      <c r="C11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="73">
         <v>4</v>
       </c>
-      <c r="E11" s="36">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37">
-        <v>0</v>
-      </c>
-      <c r="G11" s="38">
-        <v>0</v>
-      </c>
-      <c r="H11" s="39">
-        <v>0</v>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="68">
-        <v>0</v>
-      </c>
-      <c r="K11" s="69">
-        <v>0</v>
-      </c>
-      <c r="L11" s="70">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
+      <c r="E11" s="29">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <v>0</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0</v>
+      </c>
+      <c r="H11" s="32">
+        <v>0</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="61">
+        <v>0</v>
+      </c>
+      <c r="K11" s="62">
+        <v>0</v>
+      </c>
+      <c r="L11" s="63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B12" s="89" t="s">
+    <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="74">
         <v>11</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="34">
         <v>0.63636363636363635</v>
       </c>
-      <c r="F12" s="42">
-        <v>0</v>
-      </c>
-      <c r="G12" s="43">
-        <v>0</v>
-      </c>
-      <c r="H12" s="44">
-        <v>0</v>
-      </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="71">
-        <v>0</v>
-      </c>
-      <c r="K12" s="72">
-        <v>0</v>
-      </c>
-      <c r="L12" s="73">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
+      <c r="F12" s="35">
+        <v>0</v>
+      </c>
+      <c r="G12" s="36">
+        <v>0</v>
+      </c>
+      <c r="H12" s="37">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38"/>
+      <c r="J12" s="64">
+        <v>0</v>
+      </c>
+      <c r="K12" s="65">
+        <v>0</v>
+      </c>
+      <c r="L12" s="66">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B13" s="90"/>
-      <c r="C13" s="12" t="s">
+    <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="83"/>
+      <c r="C13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="82">
+      <c r="D13" s="75">
         <v>11</v>
       </c>
-      <c r="E13" s="31">
-        <v>0</v>
-      </c>
-      <c r="F13" s="32">
-        <v>0</v>
-      </c>
-      <c r="G13" s="33">
-        <v>0</v>
-      </c>
-      <c r="H13" s="46">
+      <c r="E13" s="24">
+        <v>0</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0</v>
+      </c>
+      <c r="G13" s="26">
+        <v>0</v>
+      </c>
+      <c r="H13" s="39">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="35"/>
-      <c r="J13" s="74">
-        <v>0</v>
-      </c>
-      <c r="K13" s="66">
-        <v>0</v>
-      </c>
-      <c r="L13" s="67">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="67">
+        <v>0</v>
+      </c>
+      <c r="K13" s="59">
+        <v>0</v>
+      </c>
+      <c r="L13" s="60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B14" s="90"/>
-      <c r="C14" s="12" t="s">
+    <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="83"/>
+      <c r="C14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="82">
+      <c r="D14" s="75">
         <v>5</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="24">
         <v>1.2</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="25">
         <v>0.6</v>
       </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="46">
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="39">
         <v>0.6</v>
       </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="74">
-        <v>0</v>
-      </c>
-      <c r="K14" s="66">
-        <v>0</v>
-      </c>
-      <c r="L14" s="67">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="67">
+        <v>0</v>
+      </c>
+      <c r="K14" s="59">
+        <v>0</v>
+      </c>
+      <c r="L14" s="60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="2:15" s="9" customFormat="1" ht="15.6" customHeight="1">
-      <c r="B15" s="90"/>
-      <c r="C15" s="12" t="s">
+    <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="83"/>
+      <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="82">
+      <c r="D15" s="75">
         <v>4</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="24">
         <v>1.75</v>
       </c>
-      <c r="F15" s="32">
-        <v>0</v>
-      </c>
-      <c r="G15" s="33">
-        <v>0</v>
-      </c>
-      <c r="H15" s="46">
-        <v>0</v>
-      </c>
-      <c r="I15" s="35"/>
-      <c r="J15" s="74">
-        <v>0</v>
-      </c>
-      <c r="K15" s="66">
-        <v>0</v>
-      </c>
-      <c r="L15" s="67">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
+      <c r="F15" s="25">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0</v>
+      </c>
+      <c r="I15" s="28"/>
+      <c r="J15" s="67">
+        <v>0</v>
+      </c>
+      <c r="K15" s="59">
+        <v>0</v>
+      </c>
+      <c r="L15" s="60">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="2:15" s="9" customFormat="1" ht="15.45" customHeight="1" thickBot="1">
-      <c r="B16" s="91"/>
-      <c r="C16" s="14" t="s">
+    <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="84"/>
+      <c r="C16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="76">
         <v>10</v>
       </c>
-      <c r="E16" s="36">
-        <v>0</v>
-      </c>
-      <c r="F16" s="37">
-        <v>0</v>
-      </c>
-      <c r="G16" s="47">
+      <c r="E16" s="29">
+        <v>0</v>
+      </c>
+      <c r="F16" s="30">
+        <v>0</v>
+      </c>
+      <c r="G16" s="40">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="H16" s="48">
-        <v>0</v>
-      </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="75">
+      <c r="H16" s="41">
+        <v>0</v>
+      </c>
+      <c r="I16" s="33"/>
+      <c r="J16" s="68">
         <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="K16" s="69">
-        <v>0</v>
-      </c>
-      <c r="L16" s="70">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+      <c r="K16" s="62">
+        <v>0</v>
+      </c>
+      <c r="L16" s="63">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="2:29">
-      <c r="B17" s="15"/>
-      <c r="C17" s="16" t="s">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="B17" s="12"/>
+      <c r="C17" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="77">
         <v>133</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="42">
         <v>0.22556390977443608</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="42">
         <v>0.18796992481203006</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="42">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="42">
         <v>0.22556390977443608</v>
       </c>
-      <c r="I17" s="50" t="s">
+      <c r="I17" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="61">
+      <c r="J17" s="54">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="K17" s="61">
+      <c r="K17" s="54">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="L17" s="61">
+      <c r="L17" s="54">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="M17" s="1"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
-    <row r="19" spans="2:29" hidden="1">
-      <c r="E19" s="51"/>
+    <row r="19" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="44"/>
     </row>
-    <row r="20" spans="2:29" hidden="1"/>
-    <row r="21" spans="2:29" hidden="1">
-      <c r="E21" s="54"/>
+    <row r="20" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="47"/>
     </row>
-    <row r="22" spans="2:29" hidden="1"/>
-    <row r="23" spans="2:29" hidden="1"/>
+    <row r="22" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B4:B7"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CABF64-DE01-47CF-BCF9-929CD1EAF1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD20416-B573-4919-B576-A29D94DE7D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -72,9 +72,6 @@
     <t>Seed System</t>
   </si>
   <si>
-    <t>RAFS</t>
-  </si>
-  <si>
     <t>Plant Health</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>per Program Target (target/13)</t>
   </si>
   <si>
@@ -133,6 +127,12 @@
   </si>
   <si>
     <t>Value Chain Markets and Agribusiness</t>
+  </si>
+  <si>
+    <t>Resilient Agrifood Systems</t>
+  </si>
+  <si>
+    <t>Systems Transformation</t>
   </si>
 </sst>
 </file>
@@ -1643,31 +1643,31 @@
       <c r="B3" s="3"/>
       <c r="C3" s="48"/>
       <c r="D3" s="70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="H3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="I3" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="J3" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="K3" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="L3" s="51" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="51" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="D8" s="71">
         <v>12</v>
@@ -1843,7 +1843,7 @@
     <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="80"/>
       <c r="C9" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="72">
         <v>20</v>
@@ -1877,7 +1877,7 @@
     <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="80"/>
       <c r="C10" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" s="72">
         <v>7</v>
@@ -1910,7 +1910,7 @@
     <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="81"/>
       <c r="C11" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="73">
         <v>4</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="82" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="74">
         <v>11</v>
@@ -1974,7 +1974,7 @@
     <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="83"/>
       <c r="C13" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="75">
         <v>11</v>
@@ -2005,7 +2005,7 @@
     <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="83"/>
       <c r="C14" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="75">
         <v>5</v>
@@ -2036,7 +2036,7 @@
     <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="83"/>
       <c r="C15" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="75">
         <v>4</v>
@@ -2067,7 +2067,7 @@
     <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="84"/>
       <c r="C16" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D16" s="76">
         <v>10</v>
@@ -2100,7 +2100,7 @@
     <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="12"/>
       <c r="C17" s="13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" s="77">
         <v>133</v>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD20416-B573-4919-B576-A29D94DE7D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C223FC5-1E19-4DBA-90DD-A9C0456F7BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -899,7 +899,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -974,9 +974,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -989,9 +986,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1002,9 +996,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1602,82 +1593,82 @@
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="41.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="78" customWidth="1"/>
-    <col min="5" max="11" width="8.5546875" style="45" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="46" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="75" customWidth="1"/>
+    <col min="5" max="11" width="8.5546875" style="42" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="14"/>
-      <c r="C1" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="89"/>
+      <c r="C1" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="83"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="86"/>
     </row>
     <row r="2" spans="2:12" s="17" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="90" t="s">
+      <c r="D2" s="66"/>
+      <c r="E2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="93" t="s">
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="94"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="91"/>
     </row>
     <row r="3" spans="2:12" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="70" t="s">
+      <c r="C3" s="45"/>
+      <c r="D3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="48" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="79" t="s">
+    <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="76" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="68">
         <v>7</v>
       </c>
       <c r="E4" s="19">
@@ -1693,23 +1684,25 @@
       <c r="H4" s="22">
         <v>0</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="55">
-        <v>0</v>
-      </c>
-      <c r="K4" s="56">
-        <v>0</v>
-      </c>
-      <c r="L4" s="57">
+      <c r="I4" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="52">
+        <v>0</v>
+      </c>
+      <c r="K4" s="53">
+        <v>0</v>
+      </c>
+      <c r="L4" s="54">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="80"/>
+    <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="77"/>
       <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="69">
         <v>23</v>
       </c>
       <c r="E5" s="24">
@@ -1724,26 +1717,28 @@
       <c r="H5" s="27">
         <v>0.13043478260869565</v>
       </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="58">
+      <c r="I5" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="55">
         <f>[1]Sheet1!$W$21</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="K5" s="59">
+      <c r="K5" s="56">
         <f>[1]Sheet1!$W$22</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="L5" s="60">
+      <c r="L5" s="57">
         <f>[1]Sheet1!$W$23</f>
         <v>8.6956521739130432E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="80"/>
+    <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="77"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="69">
         <v>4</v>
       </c>
       <c r="E6" s="24">
@@ -1758,60 +1753,64 @@
       <c r="H6" s="27">
         <v>0.25</v>
       </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="58">
-        <v>0</v>
-      </c>
-      <c r="K6" s="59">
-        <v>0</v>
-      </c>
-      <c r="L6" s="60">
+      <c r="I6" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="55">
+        <v>0</v>
+      </c>
+      <c r="K6" s="56">
+        <v>0</v>
+      </c>
+      <c r="L6" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="81"/>
+      <c r="B7" s="78"/>
       <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="70">
         <v>15</v>
       </c>
-      <c r="E7" s="29">
-        <v>0</v>
-      </c>
-      <c r="F7" s="30">
+      <c r="E7" s="28">
+        <v>0</v>
+      </c>
+      <c r="F7" s="29">
         <v>0.93333333333333335</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="30">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="H7" s="32">
-        <v>0</v>
-      </c>
-      <c r="I7" s="33"/>
-      <c r="J7" s="61">
+      <c r="H7" s="31">
+        <v>0</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="58">
         <f>[1]Sheet1!$AA$21</f>
         <v>0.2</v>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="59">
         <f>[1]Sheet1!$AA$22</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="60">
         <f>[1]Sheet1!$AA$23</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="79" t="s">
+    <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="76" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="71">
+      <c r="D8" s="68">
         <v>12</v>
       </c>
       <c r="E8" s="19">
@@ -1827,25 +1826,27 @@
       <c r="H8" s="22">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="55">
+      <c r="I8" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="52">
         <f>[1]Sheet1!$AC$21</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K8" s="56">
+      <c r="K8" s="53">
         <f>[1]Sheet1!$AC$22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L8" s="57">
+      <c r="L8" s="54">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="80"/>
+    <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="77"/>
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="69">
         <v>20</v>
       </c>
       <c r="E9" s="24">
@@ -1860,26 +1861,28 @@
       <c r="H9" s="27">
         <v>0.15</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="58">
+      <c r="I9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="55">
         <f>[1]Sheet1!$AE$21</f>
         <v>0.2</v>
       </c>
-      <c r="K9" s="59">
+      <c r="K9" s="56">
         <f>[1]Sheet1!$AE$22</f>
         <v>0.2</v>
       </c>
-      <c r="L9" s="60">
+      <c r="L9" s="57">
         <f>[1]Sheet1!$AE$23</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="80"/>
+    <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="77"/>
       <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="69">
         <v>7</v>
       </c>
       <c r="E10" s="24">
@@ -1894,89 +1897,95 @@
       <c r="H10" s="27">
         <v>0</v>
       </c>
-      <c r="I10" s="28"/>
-      <c r="J10" s="58">
+      <c r="I10" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="55">
         <f>[1]Sheet1!$AG$21</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="56">
         <f>[1]Sheet1!$AG$22</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="81"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="70">
         <v>4</v>
       </c>
-      <c r="E11" s="29">
-        <v>0</v>
-      </c>
-      <c r="F11" s="30">
-        <v>0</v>
-      </c>
-      <c r="G11" s="31">
-        <v>0</v>
-      </c>
-      <c r="H11" s="32">
-        <v>0</v>
-      </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="61">
-        <v>0</v>
-      </c>
-      <c r="K11" s="62">
-        <v>0</v>
-      </c>
-      <c r="L11" s="63">
+      <c r="E11" s="28">
+        <v>0</v>
+      </c>
+      <c r="F11" s="29">
+        <v>0</v>
+      </c>
+      <c r="G11" s="30">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31">
+        <v>0</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="58">
+        <v>0</v>
+      </c>
+      <c r="K11" s="59">
+        <v>0</v>
+      </c>
+      <c r="L11" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="82" t="s">
+    <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="79" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="71">
         <v>11</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="32">
         <v>0.63636363636363635</v>
       </c>
-      <c r="F12" s="35">
-        <v>0</v>
-      </c>
-      <c r="G12" s="36">
-        <v>0</v>
-      </c>
-      <c r="H12" s="37">
-        <v>0</v>
-      </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="64">
-        <v>0</v>
-      </c>
-      <c r="K12" s="65">
-        <v>0</v>
-      </c>
-      <c r="L12" s="66">
+      <c r="F12" s="33">
+        <v>0</v>
+      </c>
+      <c r="G12" s="34">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35">
+        <v>0</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="61">
+        <v>0</v>
+      </c>
+      <c r="K12" s="62">
+        <v>0</v>
+      </c>
+      <c r="L12" s="63">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="83"/>
+    <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="80"/>
       <c r="C13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="72">
         <v>11</v>
       </c>
       <c r="E13" s="24">
@@ -1988,26 +1997,28 @@
       <c r="G13" s="26">
         <v>0</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="36">
         <v>0.27272727272727271</v>
       </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="67">
-        <v>0</v>
-      </c>
-      <c r="K13" s="59">
-        <v>0</v>
-      </c>
-      <c r="L13" s="60">
+      <c r="I13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="64">
+        <v>0</v>
+      </c>
+      <c r="K13" s="56">
+        <v>0</v>
+      </c>
+      <c r="L13" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="83"/>
+    <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="80"/>
       <c r="C14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="72">
         <v>5</v>
       </c>
       <c r="E14" s="24">
@@ -2019,26 +2030,28 @@
       <c r="G14" s="26">
         <v>0</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="36">
         <v>0.6</v>
       </c>
-      <c r="I14" s="28"/>
-      <c r="J14" s="67">
-        <v>0</v>
-      </c>
-      <c r="K14" s="59">
-        <v>0</v>
-      </c>
-      <c r="L14" s="60">
+      <c r="I14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="64">
+        <v>0</v>
+      </c>
+      <c r="K14" s="56">
+        <v>0</v>
+      </c>
+      <c r="L14" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="83"/>
+    <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="80"/>
       <c r="C15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="72">
         <v>4</v>
       </c>
       <c r="E15" s="24">
@@ -2050,50 +2063,54 @@
       <c r="G15" s="26">
         <v>0</v>
       </c>
-      <c r="H15" s="39">
-        <v>0</v>
-      </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="67">
-        <v>0</v>
-      </c>
-      <c r="K15" s="59">
-        <v>0</v>
-      </c>
-      <c r="L15" s="60">
+      <c r="H15" s="36">
+        <v>0</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="64">
+        <v>0</v>
+      </c>
+      <c r="K15" s="56">
+        <v>0</v>
+      </c>
+      <c r="L15" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="84"/>
+      <c r="B16" s="81"/>
       <c r="C16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="73">
         <v>10</v>
       </c>
-      <c r="E16" s="29">
-        <v>0</v>
-      </c>
-      <c r="F16" s="30">
-        <v>0</v>
-      </c>
-      <c r="G16" s="40">
+      <c r="E16" s="28">
+        <v>0</v>
+      </c>
+      <c r="F16" s="29">
+        <v>0</v>
+      </c>
+      <c r="G16" s="37">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="H16" s="41">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33"/>
-      <c r="J16" s="68">
+      <c r="H16" s="38">
+        <v>0</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="65">
         <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="K16" s="62">
-        <v>0</v>
-      </c>
-      <c r="L16" s="63">
+      <c r="K16" s="59">
+        <v>0</v>
+      </c>
+      <c r="L16" s="60">
         <v>0</v>
       </c>
     </row>
@@ -2102,31 +2119,31 @@
       <c r="C17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="74">
         <v>133</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="39">
         <v>0.22556390977443608</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="39">
         <v>0.18796992481203006</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="39">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="39">
         <v>0.22556390977443608</v>
       </c>
-      <c r="I17" s="43" t="s">
+      <c r="I17" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="54">
+      <c r="J17" s="51">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="51">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="51">
         <v>1.8796992481203006E-3</v>
       </c>
       <c r="M17" s="2"/>
@@ -2143,11 +2160,11 @@
       <c r="X17" s="2"/>
     </row>
     <row r="19" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="44"/>
+      <c r="E19" s="41"/>
     </row>
     <row r="20" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="47"/>
+      <c r="E21" s="44"/>
     </row>
     <row r="22" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C223FC5-1E19-4DBA-90DD-A9C0456F7BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC8ECF4-8EF6-4E21-8BB5-CCCF9B1DA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
     <t>Biotech</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>Systems Transformation</t>
+  </si>
+  <si>
+    <t>Genetic Innovation</t>
   </si>
 </sst>
 </file>
@@ -1634,39 +1634,39 @@
       <c r="B3" s="3"/>
       <c r="C3" s="45"/>
       <c r="D3" s="67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="G3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="H3" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="I3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="J3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="49" t="s">
+      <c r="K3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="L3" s="48" t="s">
         <v>19</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="68">
         <v>7</v>
@@ -1675,7 +1675,7 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="21">
         <f>[1]Sheet1!$U$18</f>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="52">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="77"/>
       <c r="C5" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="69">
         <v>23</v>
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="26">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="55">
         <f>[1]Sheet1!$W$21</f>
@@ -1736,7 +1736,7 @@
     <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="77"/>
       <c r="C6" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="69">
         <v>4</v>
@@ -1745,7 +1745,7 @@
         <v>4.75</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="26">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0.25</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="55">
         <v>0</v>
@@ -1769,7 +1769,7 @@
     <row r="7" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="78"/>
       <c r="C7" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="70">
         <v>15</v>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="58">
         <f>[1]Sheet1!$AA$21</f>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="68">
         <v>12</v>
@@ -1827,7 +1827,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="52">
         <f>[1]Sheet1!$AC$21</f>
@@ -1844,7 +1844,7 @@
     <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="77"/>
       <c r="C9" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="69">
         <v>20</v>
@@ -1862,7 +1862,7 @@
         <v>0.15</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="55">
         <f>[1]Sheet1!$AE$21</f>
@@ -1880,7 +1880,7 @@
     <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="77"/>
       <c r="C10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="69">
         <v>7</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="55">
         <f>[1]Sheet1!$AG$21</f>
@@ -1915,7 +1915,7 @@
     <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="78"/>
       <c r="C11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="70">
         <v>4</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="58">
         <v>0</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="71">
         <v>11</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="61">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="80"/>
       <c r="C13" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="72">
         <v>11</v>
@@ -2001,7 +2001,7 @@
         <v>0.27272727272727271</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="64">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="80"/>
       <c r="C14" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="72">
         <v>5</v>
@@ -2034,7 +2034,7 @@
         <v>0.6</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="64">
         <v>0</v>
@@ -2049,7 +2049,7 @@
     <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="80"/>
       <c r="C15" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="72">
         <v>4</v>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="64">
         <v>0</v>
@@ -2082,7 +2082,7 @@
     <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="81"/>
       <c r="C16" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="73">
         <v>10</v>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="65">
         <f>[1]Sheet1!$AS$21</f>
@@ -2117,7 +2117,7 @@
     <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="12"/>
       <c r="C17" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="74">
         <v>133</v>
@@ -2135,7 +2135,7 @@
         <v>0.22556390977443608</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="51">
         <v>1.8796992481203006E-3</v>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC8ECF4-8EF6-4E21-8BB5-CCCF9B1DA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409F807F-927F-4219-8A59-B36E06EC9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -81,9 +81,6 @@
     <t>per Program Target (target/13)</t>
   </si>
   <si>
-    <t>Collaboration with Agriculture Research Institutions</t>
-  </si>
-  <si>
     <t>Active collaborations with scaling partners</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>Genetic Innovation</t>
+  </si>
+  <si>
+    <t>Collaboration with Advanced Research Institutions</t>
   </si>
 </sst>
 </file>
@@ -1634,36 +1634,36 @@
       <c r="B3" s="3"/>
       <c r="C3" s="45"/>
       <c r="D3" s="67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="G3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="H3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="I3" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="J3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="49" t="s">
+      <c r="K3" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="L3" s="48" t="s">
         <v>18</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
@@ -1880,7 +1880,7 @@
     <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="77"/>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="69">
         <v>7</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="71">
         <v>11</v>
@@ -1983,7 +1983,7 @@
     <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="80"/>
       <c r="C13" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="72">
         <v>11</v>
@@ -2016,7 +2016,7 @@
     <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="80"/>
       <c r="C14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="72">
         <v>5</v>
@@ -2049,7 +2049,7 @@
     <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="80"/>
       <c r="C15" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="72">
         <v>4</v>
@@ -2082,7 +2082,7 @@
     <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="81"/>
       <c r="C16" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="73">
         <v>10</v>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409F807F-927F-4219-8A59-B36E06EC9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DED675-F0C1-4284-8A20-1BA9DEE7551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t>Approved proposals with nutrition ad health components</t>
   </si>
   <si>
-    <t>FTE</t>
-  </si>
-  <si>
     <t>Natural Resource Management</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>Collaboration with Advanced Research Institutions</t>
+  </si>
+  <si>
+    <t>FTE - Number of staff</t>
   </si>
 </sst>
 </file>
@@ -235,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -891,6 +891,17 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1091,9 +1102,6 @@
     <xf numFmtId="167" fontId="7" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1161,6 +1169,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1593,51 +1604,51 @@
   <cols>
     <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="41.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="75" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" style="74" customWidth="1"/>
     <col min="5" max="11" width="8.5546875" style="42" customWidth="1"/>
     <col min="12" max="12" width="8.5546875" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="14"/>
-      <c r="C1" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="83"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="86"/>
+      <c r="C1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="85"/>
     </row>
     <row r="2" spans="2:12" s="17" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="16"/>
       <c r="C2" s="18"/>
       <c r="D2" s="66"/>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90" t="s">
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="90"/>
-      <c r="L2" s="91"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="90"/>
     </row>
     <row r="3" spans="2:12" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
       <c r="C3" s="45"/>
-      <c r="D3" s="67" t="s">
-        <v>19</v>
+      <c r="D3" s="91" t="s">
+        <v>29</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="47" t="s">
         <v>12</v>
@@ -1662,13 +1673,13 @@
       </c>
     </row>
     <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
-        <v>28</v>
+      <c r="B4" s="75" t="s">
+        <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="68">
+      <c r="D4" s="67">
         <v>7</v>
       </c>
       <c r="E4" s="19">
@@ -1698,11 +1709,11 @@
       </c>
     </row>
     <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="77"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="68">
         <v>23</v>
       </c>
       <c r="E5" s="24">
@@ -1734,11 +1745,11 @@
       </c>
     </row>
     <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="77"/>
+      <c r="B6" s="76"/>
       <c r="C6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="68">
         <v>4</v>
       </c>
       <c r="E6" s="24">
@@ -1767,11 +1778,11 @@
       </c>
     </row>
     <row r="7" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="78"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="69">
         <v>15</v>
       </c>
       <c r="E7" s="28">
@@ -1804,13 +1815,13 @@
       </c>
     </row>
     <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="76" t="s">
-        <v>26</v>
+      <c r="B8" s="75" t="s">
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="68">
+      <c r="D8" s="67">
         <v>12</v>
       </c>
       <c r="E8" s="19">
@@ -1842,11 +1853,11 @@
       </c>
     </row>
     <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="77"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="68">
         <v>20</v>
       </c>
       <c r="E9" s="24">
@@ -1878,11 +1889,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="77"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="69">
+        <v>19</v>
+      </c>
+      <c r="D10" s="68">
         <v>7</v>
       </c>
       <c r="E10" s="24">
@@ -1913,11 +1924,11 @@
       </c>
     </row>
     <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="78"/>
+      <c r="B11" s="77"/>
       <c r="C11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="69">
         <v>4</v>
       </c>
       <c r="E11" s="28">
@@ -1946,13 +1957,13 @@
       </c>
     </row>
     <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="79" t="s">
-        <v>27</v>
+      <c r="B12" s="78" t="s">
+        <v>26</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="71">
+        <v>20</v>
+      </c>
+      <c r="D12" s="70">
         <v>11</v>
       </c>
       <c r="E12" s="32">
@@ -1981,11 +1992,11 @@
       </c>
     </row>
     <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="80"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="72">
+        <v>21</v>
+      </c>
+      <c r="D13" s="71">
         <v>11</v>
       </c>
       <c r="E13" s="24">
@@ -2014,11 +2025,11 @@
       </c>
     </row>
     <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="80"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="72">
+        <v>22</v>
+      </c>
+      <c r="D14" s="71">
         <v>5</v>
       </c>
       <c r="E14" s="24">
@@ -2047,11 +2058,11 @@
       </c>
     </row>
     <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="80"/>
+      <c r="B15" s="79"/>
       <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="72">
+        <v>23</v>
+      </c>
+      <c r="D15" s="71">
         <v>4</v>
       </c>
       <c r="E15" s="24">
@@ -2080,11 +2091,11 @@
       </c>
     </row>
     <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="81"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="73">
+        <v>24</v>
+      </c>
+      <c r="D16" s="72">
         <v>10</v>
       </c>
       <c r="E16" s="28">
@@ -2119,7 +2130,7 @@
       <c r="C17" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D17" s="73">
         <v>133</v>
       </c>
       <c r="E17" s="39">

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DED675-F0C1-4284-8A20-1BA9DEE7551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FD1F69-4359-4997-A12E-3B58C328A318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$B$1:$L$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -54,12 +54,6 @@
     <t>Society Impact &amp; Inclusion</t>
   </si>
   <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -133,6 +127,12 @@
   </si>
   <si>
     <t>FTE - Number of staff</t>
+  </si>
+  <si>
+    <t>IITA Program</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
   </si>
 </sst>
 </file>
@@ -235,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -459,30 +459,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -520,19 +496,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -562,19 +525,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -648,30 +598,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -737,32 +663,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -816,92 +716,72 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -910,54 +790,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -985,44 +850,20 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1036,114 +877,56 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1155,23 +938,91 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1599,564 +1450,567 @@
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:X23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="74" customWidth="1"/>
-    <col min="5" max="11" width="8.5546875" style="42" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="41" customWidth="1"/>
+    <col min="4" max="10" width="8.5546875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="14"/>
-      <c r="C1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="85"/>
+    <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11"/>
+      <c r="B1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="52"/>
     </row>
-    <row r="2" spans="2:12" s="17" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="16"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="86" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="62"/>
+      <c r="B2" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="89" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="89"/>
-      <c r="L2" s="90"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="59"/>
     </row>
-    <row r="3" spans="2:12" s="4" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="91" t="s">
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="63"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="67">
+      <c r="C4" s="35">
         <v>7</v>
       </c>
-      <c r="E4" s="19">
+      <c r="D4" s="14">
         <v>2.4285714285714284</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="16">
         <f>[1]Sheet1!$U$18</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="H4" s="22">
-        <v>0</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="52">
-        <v>0</v>
-      </c>
-      <c r="K4" s="53">
-        <v>0</v>
-      </c>
-      <c r="L4" s="54">
+      <c r="G4" s="17">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0</v>
+      </c>
+      <c r="I4" s="67">
+        <v>0</v>
+      </c>
+      <c r="J4" s="68">
+        <v>0</v>
+      </c>
+      <c r="K4" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="76"/>
-      <c r="C5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="68">
+    <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="43"/>
+      <c r="B5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="36">
         <v>23</v>
       </c>
-      <c r="E5" s="24">
+      <c r="D5" s="19">
         <v>1</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="26">
-        <v>0</v>
-      </c>
-      <c r="H5" s="27">
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
         <v>0.13043478260869565</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="55">
+      <c r="H5" s="65">
+        <v>0</v>
+      </c>
+      <c r="I5" s="69">
         <f>[1]Sheet1!$W$21</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="K5" s="56">
+      <c r="J5" s="64">
         <f>[1]Sheet1!$W$22</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="L5" s="57">
+      <c r="K5" s="33">
         <f>[1]Sheet1!$W$23</f>
         <v>8.6956521739130432E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="76"/>
-      <c r="C6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="68">
+    <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="24">
+      <c r="C6" s="36">
+        <v>4</v>
+      </c>
+      <c r="D6" s="19">
         <v>4.75</v>
       </c>
-      <c r="F6" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="26">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27">
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22">
         <v>0.25</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="55">
-        <v>0</v>
-      </c>
-      <c r="K6" s="56">
-        <v>0</v>
-      </c>
-      <c r="L6" s="57">
+      <c r="H6" s="65">
+        <v>0</v>
+      </c>
+      <c r="I6" s="69">
+        <v>0</v>
+      </c>
+      <c r="J6" s="64">
+        <v>0</v>
+      </c>
+      <c r="K6" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="77"/>
-      <c r="C7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="69">
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44"/>
+      <c r="B7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="37">
         <v>15</v>
       </c>
-      <c r="E7" s="28">
-        <v>0</v>
-      </c>
-      <c r="F7" s="29">
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
         <v>0.93333333333333335</v>
       </c>
-      <c r="G7" s="30">
+      <c r="F7" s="21">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="H7" s="31">
-        <v>0</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="58">
+      <c r="G7" s="22">
+        <v>0</v>
+      </c>
+      <c r="H7" s="65">
+        <v>0</v>
+      </c>
+      <c r="I7" s="69">
         <f>[1]Sheet1!$AA$21</f>
         <v>0.2</v>
       </c>
-      <c r="K7" s="59">
+      <c r="J7" s="64">
         <f>[1]Sheet1!$AA$22</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="L7" s="60">
+      <c r="K7" s="33">
         <f>[1]Sheet1!$AA$23</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="67">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="35">
         <v>12</v>
       </c>
-      <c r="E8" s="19">
+      <c r="D8" s="19">
         <v>1.5</v>
       </c>
-      <c r="F8" s="20">
+      <c r="E8" s="20">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G8" s="21">
+      <c r="F8" s="21">
         <f>[1]Sheet1!$AC$18</f>
         <v>0.25</v>
       </c>
-      <c r="H8" s="22">
+      <c r="G8" s="22">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="52">
+      <c r="H8" s="65">
+        <v>0</v>
+      </c>
+      <c r="I8" s="69">
         <f>[1]Sheet1!$AC$21</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K8" s="53">
+      <c r="J8" s="64">
         <f>[1]Sheet1!$AC$22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L8" s="54">
+      <c r="K8" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="76"/>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="68">
+    <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="36">
         <v>20</v>
       </c>
-      <c r="E9" s="24">
+      <c r="D9" s="19">
         <v>2.15</v>
       </c>
-      <c r="F9" s="25">
+      <c r="E9" s="20">
         <v>0.85</v>
       </c>
-      <c r="G9" s="26">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27">
+      <c r="F9" s="21">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22">
         <v>0.15</v>
       </c>
-      <c r="I9" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="55">
+      <c r="H9" s="65">
+        <v>0</v>
+      </c>
+      <c r="I9" s="69">
         <f>[1]Sheet1!$AE$21</f>
         <v>0.2</v>
       </c>
-      <c r="K9" s="56">
+      <c r="J9" s="64">
         <f>[1]Sheet1!$AE$22</f>
         <v>0.2</v>
       </c>
-      <c r="L9" s="57">
+      <c r="K9" s="33">
         <f>[1]Sheet1!$AE$23</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="76"/>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="68">
+    <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="36">
         <v>7</v>
       </c>
-      <c r="E10" s="24">
-        <v>0</v>
-      </c>
-      <c r="F10" s="25">
+      <c r="D10" s="19">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20">
         <v>0.42857142857142855</v>
       </c>
-      <c r="G10" s="26">
-        <v>0</v>
-      </c>
-      <c r="H10" s="27">
-        <v>0</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="55">
+      <c r="F10" s="21">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0</v>
+      </c>
+      <c r="H10" s="65">
+        <v>0</v>
+      </c>
+      <c r="I10" s="69">
         <f>[1]Sheet1!$AG$21</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="K10" s="56">
+      <c r="J10" s="64">
         <f>[1]Sheet1!$AG$22</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="L10" s="57">
+      <c r="K10" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="77"/>
-      <c r="C11" s="8" t="s">
+    <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="44"/>
+      <c r="B11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="37">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0</v>
+      </c>
+      <c r="H11" s="65">
+        <v>0</v>
+      </c>
+      <c r="I11" s="69">
+        <v>0</v>
+      </c>
+      <c r="J11" s="64">
+        <v>0</v>
+      </c>
+      <c r="K11" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="38">
+        <v>11</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25">
+        <v>0</v>
+      </c>
+      <c r="H12" s="65">
+        <v>0</v>
+      </c>
+      <c r="I12" s="70">
+        <v>0</v>
+      </c>
+      <c r="J12" s="64">
+        <v>0</v>
+      </c>
+      <c r="K12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46"/>
+      <c r="B13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="39">
+        <v>11</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="H13" s="65">
+        <v>0</v>
+      </c>
+      <c r="I13" s="70">
+        <v>0</v>
+      </c>
+      <c r="J13" s="64">
+        <v>0</v>
+      </c>
+      <c r="K13" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
+      <c r="B14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="39">
+        <v>5</v>
+      </c>
+      <c r="D14" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="F14" s="21">
+        <v>0</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="H14" s="65">
+        <v>0</v>
+      </c>
+      <c r="I14" s="70">
+        <v>0</v>
+      </c>
+      <c r="J14" s="64">
+        <v>0</v>
+      </c>
+      <c r="K14" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46"/>
+      <c r="B15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="39">
+        <v>4</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1.75</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25">
+        <v>0</v>
+      </c>
+      <c r="H15" s="65">
+        <v>0</v>
+      </c>
+      <c r="I15" s="70">
+        <v>0</v>
+      </c>
+      <c r="J15" s="64">
+        <v>0</v>
+      </c>
+      <c r="K15" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="40">
         <v>10</v>
       </c>
-      <c r="D11" s="69">
-        <v>4</v>
-      </c>
-      <c r="E11" s="28">
-        <v>0</v>
-      </c>
-      <c r="F11" s="29">
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <v>0</v>
-      </c>
-      <c r="H11" s="31">
-        <v>0</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="58">
-        <v>0</v>
-      </c>
-      <c r="K11" s="59">
-        <v>0</v>
-      </c>
-      <c r="L11" s="60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="70">
-        <v>11</v>
-      </c>
-      <c r="E12" s="32">
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="F12" s="33">
-        <v>0</v>
-      </c>
-      <c r="G12" s="34">
-        <v>0</v>
-      </c>
-      <c r="H12" s="35">
-        <v>0</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="61">
-        <v>0</v>
-      </c>
-      <c r="K12" s="62">
-        <v>0</v>
-      </c>
-      <c r="L12" s="63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="79"/>
-      <c r="C13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="71">
-        <v>11</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0</v>
-      </c>
-      <c r="F13" s="25">
-        <v>0</v>
-      </c>
-      <c r="G13" s="26">
-        <v>0</v>
-      </c>
-      <c r="H13" s="36">
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="64">
-        <v>0</v>
-      </c>
-      <c r="K13" s="56">
-        <v>0</v>
-      </c>
-      <c r="L13" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="79"/>
-      <c r="C14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="71">
-        <v>5</v>
-      </c>
-      <c r="E14" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="F14" s="25">
-        <v>0.6</v>
-      </c>
-      <c r="G14" s="26">
-        <v>0</v>
-      </c>
-      <c r="H14" s="36">
-        <v>0.6</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="64">
-        <v>0</v>
-      </c>
-      <c r="K14" s="56">
-        <v>0</v>
-      </c>
-      <c r="L14" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" s="6" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="79"/>
-      <c r="C15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="71">
-        <v>4</v>
-      </c>
-      <c r="E15" s="24">
-        <v>1.75</v>
-      </c>
-      <c r="F15" s="25">
-        <v>0</v>
-      </c>
-      <c r="G15" s="26">
-        <v>0</v>
-      </c>
-      <c r="H15" s="36">
-        <v>0</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="64">
-        <v>0</v>
-      </c>
-      <c r="K15" s="56">
-        <v>0</v>
-      </c>
-      <c r="L15" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" s="6" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="80"/>
-      <c r="C16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="72">
-        <v>10</v>
-      </c>
-      <c r="E16" s="28">
-        <v>0</v>
-      </c>
-      <c r="F16" s="29">
-        <v>0</v>
-      </c>
-      <c r="G16" s="37">
+      <c r="D16" s="23">
+        <v>0</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0</v>
+      </c>
+      <c r="F16" s="26">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="H16" s="38">
-        <v>0</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="65">
+      <c r="G16" s="27">
+        <v>0</v>
+      </c>
+      <c r="H16" s="66">
+        <v>0</v>
+      </c>
+      <c r="I16" s="71">
         <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="K16" s="59">
-        <v>0</v>
-      </c>
-      <c r="L16" s="60">
+      <c r="J16" s="72">
+        <v>0</v>
+      </c>
+      <c r="K16" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="73">
+    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="61"/>
+      <c r="B17" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="78">
         <v>133</v>
       </c>
-      <c r="E17" s="39">
+      <c r="D17" s="79">
         <v>0.22556390977443608</v>
       </c>
-      <c r="F17" s="39">
+      <c r="E17" s="79">
         <v>0.18796992481203006</v>
       </c>
-      <c r="G17" s="39">
+      <c r="F17" s="79">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="39">
+      <c r="G17" s="79">
         <v>0.22556390977443608</v>
       </c>
-      <c r="I17" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="51">
+      <c r="H17" s="80">
+        <v>0</v>
+      </c>
+      <c r="I17" s="81">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="K17" s="51">
+      <c r="J17" s="81">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="L17" s="51">
+      <c r="K17" s="82">
         <v>1.8796992481203006E-3</v>
       </c>
+      <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2168,28 +2022,44 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
     </row>
-    <row r="19" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="41"/>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="60"/>
     </row>
-    <row r="20" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:24" hidden="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="44"/>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="28"/>
     </row>
-    <row r="22" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:24" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="31"/>
+    </row>
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="J2:L2"/>
+  <mergeCells count="8">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4:D16">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$17/2"/>
+        <cfvo type="formula" val="$D$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2201,7 +2071,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2213,7 +2083,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2224,12 +2094,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="41">
+  <conditionalFormatting sqref="I4:I16">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$H$17/2"/>
-        <cfvo type="formula" val="$H$17"/>
+        <cfvo type="formula" val="$I$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -2237,7 +2107,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2249,23 +2119,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$L$17/2"/>
-        <cfvo type="formula" val="$L$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FD1F69-4359-4997-A12E-3B58C328A318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A23FC98-4CA5-44B4-9DBB-5305CC6784EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>KPI by FTE</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -877,15 +880,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -905,97 +899,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1010,7 +923,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -1023,6 +936,75 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1455,91 +1437,91 @@
   <cols>
     <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.21875" style="41" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="38" customWidth="1"/>
     <col min="4" max="10" width="8.5546875" style="29" customWidth="1"/>
     <col min="11" max="11" width="8.5546875" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
-      <c r="B1" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="63"/>
     </row>
     <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="62"/>
-      <c r="B2" s="53" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="58"/>
-      <c r="K2" s="59"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="63"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74" t="s">
+      <c r="A3" s="72"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="75" t="s">
+      <c r="I3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="75" t="s">
+      <c r="J3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="45" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="53" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="32">
         <v>7</v>
       </c>
       <c r="D4" s="14">
         <v>2.4285714285714284</v>
       </c>
-      <c r="E4" s="15">
-        <v>0</v>
+      <c r="E4" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="F4" s="16">
         <f>[1]Sheet1!$U$18</f>
@@ -1548,32 +1530,32 @@
       <c r="G4" s="17">
         <v>0</v>
       </c>
-      <c r="H4" s="18">
-        <v>0</v>
-      </c>
-      <c r="I4" s="67">
-        <v>0</v>
-      </c>
-      <c r="J4" s="68">
-        <v>0</v>
-      </c>
-      <c r="K4" s="32">
+      <c r="H4" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17">
+        <v>0</v>
+      </c>
+      <c r="K4" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
+      <c r="A5" s="54"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="33">
         <v>23</v>
       </c>
       <c r="D5" s="19">
         <v>1</v>
       </c>
-      <c r="E5" s="20">
-        <v>0</v>
+      <c r="E5" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="F5" s="21">
         <v>0</v>
@@ -1581,35 +1563,35 @@
       <c r="G5" s="22">
         <v>0.13043478260869565</v>
       </c>
-      <c r="H5" s="65">
-        <v>0</v>
-      </c>
-      <c r="I5" s="69">
+      <c r="H5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="19">
         <f>[1]Sheet1!$W$21</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="22">
         <f>[1]Sheet1!$W$22</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="41">
         <f>[1]Sheet1!$W$23</f>
         <v>8.6956521739130432E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
+      <c r="A6" s="54"/>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="33">
         <v>4</v>
       </c>
       <c r="D6" s="19">
         <v>4.75</v>
       </c>
-      <c r="E6" s="20">
-        <v>0</v>
+      <c r="E6" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="F6" s="21">
         <v>0</v>
@@ -1617,25 +1599,25 @@
       <c r="G6" s="22">
         <v>0.25</v>
       </c>
-      <c r="H6" s="65">
-        <v>0</v>
-      </c>
-      <c r="I6" s="69">
-        <v>0</v>
-      </c>
-      <c r="J6" s="64">
-        <v>0</v>
-      </c>
-      <c r="K6" s="33">
+      <c r="H6" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0</v>
+      </c>
+      <c r="J6" s="22">
+        <v>0</v>
+      </c>
+      <c r="K6" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="34">
         <v>15</v>
       </c>
       <c r="D7" s="19">
@@ -1651,30 +1633,30 @@
       <c r="G7" s="22">
         <v>0</v>
       </c>
-      <c r="H7" s="65">
-        <v>0</v>
-      </c>
-      <c r="I7" s="69">
+      <c r="H7" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="19">
         <f>[1]Sheet1!$AA$21</f>
         <v>0.2</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="22">
         <f>[1]Sheet1!$AA$22</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="41">
         <f>[1]Sheet1!$AA$23</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="53" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="32">
         <v>12</v>
       </c>
       <c r="D8" s="19">
@@ -1690,27 +1672,27 @@
       <c r="G8" s="22">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H8" s="65">
-        <v>0</v>
-      </c>
-      <c r="I8" s="69">
+      <c r="H8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="19">
         <f>[1]Sheet1!$AC$21</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="22">
         <f>[1]Sheet1!$AC$22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K8" s="33">
+      <c r="K8" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="33">
         <v>20</v>
       </c>
       <c r="D9" s="19">
@@ -1725,28 +1707,28 @@
       <c r="G9" s="22">
         <v>0.15</v>
       </c>
-      <c r="H9" s="65">
-        <v>0</v>
-      </c>
-      <c r="I9" s="69">
+      <c r="H9" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="19">
         <f>[1]Sheet1!$AE$21</f>
         <v>0.2</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="22">
         <f>[1]Sheet1!$AE$22</f>
         <v>0.2</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9" s="41">
         <f>[1]Sheet1!$AE$23</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="33">
         <v>7</v>
       </c>
       <c r="D10" s="19">
@@ -1761,27 +1743,27 @@
       <c r="G10" s="22">
         <v>0</v>
       </c>
-      <c r="H10" s="65">
-        <v>0</v>
-      </c>
-      <c r="I10" s="69">
+      <c r="H10" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="19">
         <f>[1]Sheet1!$AG$21</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="22">
         <f>[1]Sheet1!$AG$22</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="34">
         <v>4</v>
       </c>
       <c r="D11" s="19">
@@ -1796,27 +1778,27 @@
       <c r="G11" s="22">
         <v>0</v>
       </c>
-      <c r="H11" s="65">
-        <v>0</v>
-      </c>
-      <c r="I11" s="69">
-        <v>0</v>
-      </c>
-      <c r="J11" s="64">
-        <v>0</v>
-      </c>
-      <c r="K11" s="33">
+      <c r="H11" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0</v>
+      </c>
+      <c r="J11" s="22">
+        <v>0</v>
+      </c>
+      <c r="K11" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="56" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="35">
         <v>11</v>
       </c>
       <c r="D12" s="19">
@@ -1831,25 +1813,25 @@
       <c r="G12" s="25">
         <v>0</v>
       </c>
-      <c r="H12" s="65">
-        <v>0</v>
-      </c>
-      <c r="I12" s="70">
-        <v>0</v>
-      </c>
-      <c r="J12" s="64">
-        <v>0</v>
-      </c>
-      <c r="K12" s="33">
+      <c r="H12" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="73">
+        <v>0</v>
+      </c>
+      <c r="J12" s="22">
+        <v>0</v>
+      </c>
+      <c r="K12" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
+      <c r="A13" s="57"/>
       <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="36">
         <v>11</v>
       </c>
       <c r="D13" s="19">
@@ -1864,25 +1846,25 @@
       <c r="G13" s="25">
         <v>0.27272727272727271</v>
       </c>
-      <c r="H13" s="65">
-        <v>0</v>
-      </c>
-      <c r="I13" s="70">
-        <v>0</v>
-      </c>
-      <c r="J13" s="64">
-        <v>0</v>
-      </c>
-      <c r="K13" s="33">
+      <c r="H13" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="73">
+        <v>0</v>
+      </c>
+      <c r="J13" s="22">
+        <v>0</v>
+      </c>
+      <c r="K13" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="57"/>
       <c r="B14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="36">
         <v>5</v>
       </c>
       <c r="D14" s="19">
@@ -1897,25 +1879,25 @@
       <c r="G14" s="25">
         <v>0.6</v>
       </c>
-      <c r="H14" s="65">
-        <v>0</v>
-      </c>
-      <c r="I14" s="70">
-        <v>0</v>
-      </c>
-      <c r="J14" s="64">
-        <v>0</v>
-      </c>
-      <c r="K14" s="33">
+      <c r="H14" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="73">
+        <v>0</v>
+      </c>
+      <c r="J14" s="22">
+        <v>0</v>
+      </c>
+      <c r="K14" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
+      <c r="A15" s="57"/>
       <c r="B15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="36">
         <v>4</v>
       </c>
       <c r="D15" s="19">
@@ -1930,25 +1912,25 @@
       <c r="G15" s="25">
         <v>0</v>
       </c>
-      <c r="H15" s="65">
-        <v>0</v>
-      </c>
-      <c r="I15" s="70">
-        <v>0</v>
-      </c>
-      <c r="J15" s="64">
-        <v>0</v>
-      </c>
-      <c r="K15" s="33">
+      <c r="H15" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="73">
+        <v>0</v>
+      </c>
+      <c r="J15" s="22">
+        <v>0</v>
+      </c>
+      <c r="K15" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="37">
         <v>10</v>
       </c>
       <c r="D16" s="23">
@@ -1964,50 +1946,50 @@
       <c r="G16" s="27">
         <v>0</v>
       </c>
-      <c r="H16" s="66">
-        <v>0</v>
-      </c>
-      <c r="I16" s="71">
+      <c r="H16" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="74">
         <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="J16" s="72">
-        <v>0</v>
-      </c>
-      <c r="K16" s="34">
+      <c r="J16" s="75">
+        <v>0</v>
+      </c>
+      <c r="K16" s="42">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="61"/>
-      <c r="B17" s="77" t="s">
+      <c r="A17" s="69"/>
+      <c r="B17" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="48">
         <v>133</v>
       </c>
-      <c r="D17" s="79">
+      <c r="D17" s="49">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="79">
+      <c r="E17" s="49">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="49">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="49">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="80">
-        <v>0</v>
-      </c>
-      <c r="I17" s="81">
+      <c r="H17" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="51">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="J17" s="81">
+      <c r="J17" s="51">
         <v>1.8796992481203006E-3</v>
       </c>
-      <c r="K17" s="82">
+      <c r="K17" s="52">
         <v>1.8796992481203006E-3</v>
       </c>
       <c r="L17" s="2"/>
@@ -2024,7 +2006,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="70"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="D19" s="28"/>
@@ -2037,14 +2019,14 @@
     <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="38">

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A23FC98-4CA5-44B4-9DBB-5305CC6784EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFF8413-B0E1-45A7-9AE2-CE163334CE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -142,10 +142,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -793,7 +792,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,18 +923,65 @@
       <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -955,56 +1001,8 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1444,40 +1442,40 @@
   <sheetData>
     <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
-      <c r="B1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="63"/>
+      <c r="B1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="58"/>
     </row>
     <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71"/>
+      <c r="A2" s="66"/>
       <c r="B2" s="39" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="40"/>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="67" t="s">
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="68"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="72"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="43"/>
       <c r="C3" s="44" t="s">
         <v>27</v>
@@ -1508,7 +1506,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="68" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1544,7 +1542,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1580,7 +1578,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1613,7 +1611,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1650,7 +1648,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="68" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1688,7 +1686,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="69"/>
       <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1724,7 +1722,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1759,7 +1757,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55"/>
+      <c r="A11" s="70"/>
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1792,7 +1790,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="71" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1816,7 +1814,7 @@
       <c r="H12" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="73">
+      <c r="I12" s="50">
         <v>0</v>
       </c>
       <c r="J12" s="22">
@@ -1827,7 +1825,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
@@ -1849,7 +1847,7 @@
       <c r="H13" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="73">
+      <c r="I13" s="50">
         <v>0</v>
       </c>
       <c r="J13" s="22">
@@ -1860,7 +1858,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
+      <c r="A14" s="72"/>
       <c r="B14" s="8" t="s">
         <v>20</v>
       </c>
@@ -1882,7 +1880,7 @@
       <c r="H14" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="73">
+      <c r="I14" s="50">
         <v>0</v>
       </c>
       <c r="J14" s="22">
@@ -1893,7 +1891,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
+      <c r="A15" s="72"/>
       <c r="B15" s="8" t="s">
         <v>21</v>
       </c>
@@ -1915,7 +1913,7 @@
       <c r="H15" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="73">
+      <c r="I15" s="50">
         <v>0</v>
       </c>
       <c r="J15" s="22">
@@ -1926,7 +1924,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
+      <c r="A16" s="73"/>
       <c r="B16" s="10" t="s">
         <v>22</v>
       </c>
@@ -1949,11 +1947,11 @@
       <c r="H16" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="74">
+      <c r="I16" s="51">
         <f>[1]Sheet1!$AS$21</f>
         <v>0.1</v>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="52">
         <v>0</v>
       </c>
       <c r="K16" s="42">
@@ -1961,36 +1959,36 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="69"/>
+      <c r="A17" s="64"/>
       <c r="B17" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="53">
         <v>133</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="48">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="48">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="48">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="48">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="51">
-        <v>1.8796992481203006E-3</v>
-      </c>
-      <c r="J17" s="51">
-        <v>1.8796992481203006E-3</v>
-      </c>
-      <c r="K17" s="52">
-        <v>1.8796992481203006E-3</v>
+      <c r="I17" s="48">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="48">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="74">
+        <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2006,7 +2004,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="70"/>
+      <c r="A18" s="65"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="D19" s="28"/>
@@ -2019,14 +2017,14 @@
     <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:K2"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="38">

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFF8413-B0E1-45A7-9AE2-CE163334CE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAC1A4-DB36-42C1-B593-89F3A8359764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -123,12 +123,6 @@
     <t>Genetic Innovation</t>
   </si>
   <si>
-    <t>Collaboration with Advanced Research Institutions</t>
-  </si>
-  <si>
-    <t>FTE - Number of staff</t>
-  </si>
-  <si>
     <t>IITA Program</t>
   </si>
   <si>
@@ -136,6 +130,12 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>USD (million)</t>
+  </si>
+  <si>
+    <t>Collaboration with Agriculture Research Institutions</t>
   </si>
 </sst>
 </file>
@@ -145,7 +145,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -792,7 +792,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -879,29 +879,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -912,15 +912,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -938,8 +929,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1000,9 +1021,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1053,54 +1071,6 @@
           </cell>
           <cell r="AS18">
             <v>0.1</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="W21">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-          <cell r="AA21">
-            <v>0.2</v>
-          </cell>
-          <cell r="AC21">
-            <v>8.3333333333333329E-2</v>
-          </cell>
-          <cell r="AE21">
-            <v>0.2</v>
-          </cell>
-          <cell r="AG21">
-            <v>0.5714285714285714</v>
-          </cell>
-          <cell r="AS21">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="W22">
-            <v>4.3478260869565216E-2</v>
-          </cell>
-          <cell r="AA22">
-            <v>0.13333333333333333</v>
-          </cell>
-          <cell r="AC22">
-            <v>8.3333333333333329E-2</v>
-          </cell>
-          <cell r="AE22">
-            <v>0.2</v>
-          </cell>
-          <cell r="AG22">
-            <v>0.7142857142857143</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="W23">
-            <v>8.6956521739130432E-2</v>
-          </cell>
-          <cell r="AA23">
-            <v>6.6666666666666666E-2</v>
-          </cell>
-          <cell r="AE23">
-            <v>0.05</v>
           </cell>
         </row>
       </sheetData>
@@ -1433,84 +1403,84 @@
   <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.21875" style="38" customWidth="1"/>
-    <col min="4" max="10" width="8.5546875" style="29" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" style="30" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" style="38" customWidth="1"/>
+    <col min="4" max="10" width="7.21875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="7.21875" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
-      <c r="B1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="58"/>
+      <c r="B1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="40"/>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62" t="s">
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="70"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="C3" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="54" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="75" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="32">
         <v>7</v>
@@ -1519,7 +1489,7 @@
         <v>2.4285714285714284</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" s="16">
         <f>[1]Sheet1!$U$18</f>
@@ -1529,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" s="14">
         <v>0</v>
@@ -1542,7 +1512,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1553,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F5" s="21">
         <v>0</v>
@@ -1562,23 +1532,20 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="19">
-        <f>[1]Sheet1!$W$21</f>
-        <v>8.6956521739130432E-2</v>
-      </c>
-      <c r="J5" s="22">
-        <f>[1]Sheet1!$W$22</f>
-        <v>4.3478260869565216E-2</v>
-      </c>
-      <c r="K5" s="41">
-        <f>[1]Sheet1!$W$23</f>
-        <v>8.6956521739130432E-2</v>
+        <v>28</v>
+      </c>
+      <c r="I5" s="55">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J5" s="56">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K5" s="57">
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="69"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1589,7 +1556,7 @@
         <v>4.75</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F6" s="21">
         <v>0</v>
@@ -1598,7 +1565,7 @@
         <v>0.25</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I6" s="19">
         <v>0</v>
@@ -1611,7 +1578,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="70"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1632,23 +1599,20 @@
         <v>0</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="19">
-        <f>[1]Sheet1!$AA$21</f>
-        <v>0.2</v>
-      </c>
-      <c r="J7" s="22">
-        <f>[1]Sheet1!$AA$22</f>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="K7" s="41">
-        <f>[1]Sheet1!$AA$23</f>
-        <v>6.6666666666666666E-2</v>
+        <v>28</v>
+      </c>
+      <c r="I7" s="55">
+        <v>0.43</v>
+      </c>
+      <c r="J7" s="56">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K7" s="57">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="75" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1671,22 +1635,20 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="H8" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="19">
-        <f>[1]Sheet1!$AC$21</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="J8" s="22">
-        <f>[1]Sheet1!$AC$22</f>
-        <v>8.3333333333333329E-2</v>
+        <v>28</v>
+      </c>
+      <c r="I8" s="55">
+        <v>0.33</v>
+      </c>
+      <c r="J8" s="56">
+        <v>0.33</v>
       </c>
       <c r="K8" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="69"/>
+      <c r="A9" s="76"/>
       <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1706,23 +1668,20 @@
         <v>0.15</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="19">
-        <f>[1]Sheet1!$AE$21</f>
-        <v>0.2</v>
-      </c>
-      <c r="J9" s="22">
-        <f>[1]Sheet1!$AE$22</f>
-        <v>0.2</v>
-      </c>
-      <c r="K9" s="41">
-        <f>[1]Sheet1!$AE$23</f>
-        <v>0.05</v>
+        <v>28</v>
+      </c>
+      <c r="I9" s="55">
+        <v>0.44</v>
+      </c>
+      <c r="J9" s="56">
+        <v>0.44</v>
+      </c>
+      <c r="K9" s="57">
+        <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="69"/>
+      <c r="A10" s="76"/>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1742,22 +1701,20 @@
         <v>0</v>
       </c>
       <c r="H10" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="19">
-        <f>[1]Sheet1!$AG$21</f>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J10" s="22">
-        <f>[1]Sheet1!$AG$22</f>
-        <v>0.7142857142857143</v>
+        <v>28</v>
+      </c>
+      <c r="I10" s="55">
+        <v>0.71</v>
+      </c>
+      <c r="J10" s="56">
+        <v>0.71</v>
       </c>
       <c r="K10" s="41">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="70"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1777,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" s="19">
         <v>0</v>
@@ -1790,7 +1747,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="78" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1812,9 +1769,9 @@
         <v>0</v>
       </c>
       <c r="H12" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="50">
+        <v>28</v>
+      </c>
+      <c r="I12" s="47">
         <v>0</v>
       </c>
       <c r="J12" s="22">
@@ -1825,7 +1782,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
@@ -1845,9 +1802,9 @@
         <v>0.27272727272727271</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="50">
+        <v>28</v>
+      </c>
+      <c r="I13" s="47">
         <v>0</v>
       </c>
       <c r="J13" s="22">
@@ -1858,7 +1815,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="8" t="s">
         <v>20</v>
       </c>
@@ -1878,9 +1835,9 @@
         <v>0.6</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="50">
+        <v>28</v>
+      </c>
+      <c r="I14" s="47">
         <v>0</v>
       </c>
       <c r="J14" s="22">
@@ -1891,7 +1848,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="8" t="s">
         <v>21</v>
       </c>
@@ -1911,9 +1868,9 @@
         <v>0</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="50">
+        <v>28</v>
+      </c>
+      <c r="I15" s="47">
         <v>0</v>
       </c>
       <c r="J15" s="22">
@@ -1924,7 +1881,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
+      <c r="A16" s="80"/>
       <c r="B16" s="10" t="s">
         <v>22</v>
       </c>
@@ -1945,13 +1902,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="51">
-        <f>[1]Sheet1!$AS$21</f>
-        <v>0.1</v>
-      </c>
-      <c r="J16" s="52">
+        <v>28</v>
+      </c>
+      <c r="I16" s="48">
+        <v>1</v>
+      </c>
+      <c r="J16" s="49">
         <v>0</v>
       </c>
       <c r="K16" s="42">
@@ -1959,35 +1915,35 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="64"/>
-      <c r="B17" s="47" t="s">
+      <c r="A17" s="71"/>
+      <c r="B17" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="50">
         <v>133</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="45">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="45">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="45">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="45">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="48">
+      <c r="H17" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="58">
         <v>0.25</v>
       </c>
-      <c r="J17" s="48">
+      <c r="J17" s="59">
         <v>0.25</v>
       </c>
-      <c r="K17" s="74">
+      <c r="K17" s="60">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -2004,7 +1960,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="65"/>
+      <c r="A18" s="72"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="D19" s="28"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CAC1A4-DB36-42C1-B593-89F3A8359764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6871B9B5-54DC-4EDC-B009-27F61DB3DDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -792,7 +792,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -921,9 +921,6 @@
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1412,71 +1409,71 @@
   <sheetData>
     <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11"/>
-      <c r="B1" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="39" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="40"/>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="69" t="s">
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="69"/>
-      <c r="K2" s="70"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="54" t="s">
+      <c r="K3" s="53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1512,7 +1509,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1534,18 +1531,18 @@
       <c r="H5" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="55">
+      <c r="I5" s="54">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="56">
+      <c r="J5" s="55">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="57">
+      <c r="K5" s="56">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1578,7 +1575,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1601,18 +1598,18 @@
       <c r="H7" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="54">
         <v>0.43</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="55">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="57">
+      <c r="K7" s="56">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="74" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1637,10 +1634,10 @@
       <c r="H8" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="54">
         <v>0.33</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="55">
         <v>0.33</v>
       </c>
       <c r="K8" s="41">
@@ -1648,7 +1645,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1670,18 +1667,18 @@
       <c r="H9" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="54">
         <v>0.44</v>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="55">
         <v>0.44</v>
       </c>
-      <c r="K9" s="57">
+      <c r="K9" s="56">
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1703,10 +1700,10 @@
       <c r="H10" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="54">
         <v>0.71</v>
       </c>
-      <c r="J10" s="56">
+      <c r="J10" s="55">
         <v>0.71</v>
       </c>
       <c r="K10" s="41">
@@ -1714,7 +1711,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
+      <c r="A11" s="76"/>
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1747,7 +1744,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1782,7 +1779,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79"/>
+      <c r="A13" s="78"/>
       <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
@@ -1815,7 +1812,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79"/>
+      <c r="A14" s="78"/>
       <c r="B14" s="8" t="s">
         <v>20</v>
       </c>
@@ -1848,7 +1845,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
+      <c r="A15" s="78"/>
       <c r="B15" s="8" t="s">
         <v>21</v>
       </c>
@@ -1881,7 +1878,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="80"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="10" t="s">
         <v>22</v>
       </c>
@@ -1904,10 +1901,10 @@
       <c r="H16" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="54">
         <v>1</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="48">
         <v>0</v>
       </c>
       <c r="K16" s="42">
@@ -1915,11 +1912,11 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="71"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="49">
         <v>133</v>
       </c>
       <c r="D17" s="45">
@@ -1937,13 +1934,13 @@
       <c r="H17" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="57">
         <v>0.25</v>
       </c>
-      <c r="J17" s="59">
+      <c r="J17" s="58">
         <v>0.25</v>
       </c>
-      <c r="K17" s="60">
+      <c r="K17" s="59">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -1960,7 +1957,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="D19" s="28"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6871B9B5-54DC-4EDC-B009-27F61DB3DDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2379D7E6-3D1F-48FF-9DDA-DDCC4B5B422B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
@@ -132,10 +132,10 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>USD (million)</t>
-  </si>
-  <si>
     <t>Collaboration with Agriculture Research Institutions</t>
+  </si>
+  <si>
+    <t>Full Time Equivalent (FTE)</t>
   </si>
 </sst>
 </file>
@@ -143,9 +143,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -217,7 +217,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,8 +236,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="42">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -302,21 +308,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -328,51 +319,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -440,32 +386,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF00B050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,21 +406,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FF00B050"/>
@@ -511,13 +416,152 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color theme="1"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -528,72 +572,92 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -603,8 +667,42 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -612,176 +710,43 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -789,35 +754,17 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -837,132 +784,157 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,46 +949,49 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1043,19 +1018,14 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Chart1"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="12">
-          <cell r="I12">
-            <v>1.4999999999999999E-2</v>
-          </cell>
-        </row>
         <row r="18">
           <cell r="U18">
             <v>0.14285714285714285</v>
@@ -1398,549 +1368,549 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.88671875" style="38" customWidth="1"/>
-    <col min="4" max="10" width="7.21875" style="29" customWidth="1"/>
-    <col min="11" max="11" width="7.21875" style="30" customWidth="1"/>
+    <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.36328125" style="21" customWidth="1"/>
+    <col min="4" max="10" width="7.1796875" style="18" customWidth="1"/>
+    <col min="11" max="11" width="7.1796875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11"/>
-      <c r="B1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="64"/>
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="5"/>
+      <c r="B1" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="64"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="67"/>
     </row>
-    <row r="2" spans="1:11" s="13" customFormat="1" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="76"/>
+      <c r="B2" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="65" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68" t="s">
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="69"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="73"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="73"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="50" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="40">
         <v>7</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="50">
         <v>2.4285714285714284</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="52">
         <f>[1]Sheet1!$U$18</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="G4" s="17">
-        <v>0</v>
-      </c>
-      <c r="H4" s="18" t="s">
+      <c r="G4" s="53">
+        <v>0</v>
+      </c>
+      <c r="H4" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="14">
-        <v>0</v>
-      </c>
-      <c r="J4" s="17">
-        <v>0</v>
-      </c>
-      <c r="K4" s="18">
+      <c r="I4" s="55">
+        <v>0</v>
+      </c>
+      <c r="J4" s="56">
+        <v>0</v>
+      </c>
+      <c r="K4" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="41">
         <v>23</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="8">
         <v>1</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="21">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
         <v>0.13043478260869565</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="43">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="55">
+      <c r="J5" s="44">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="45">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79"/>
+      <c r="B6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="41">
         <v>4</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="8">
         <v>4.75</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22">
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
         <v>0.25</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="19">
-        <v>0</v>
-      </c>
-      <c r="J6" s="22">
-        <v>0</v>
-      </c>
-      <c r="K6" s="41">
+      <c r="I6" s="43">
+        <v>0</v>
+      </c>
+      <c r="J6" s="44">
+        <v>0</v>
+      </c>
+      <c r="K6" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="76"/>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="80"/>
+      <c r="B7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="42">
         <v>15</v>
       </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="20">
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
         <v>0.93333333333333335</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="58">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="G7" s="22">
-        <v>0</v>
-      </c>
-      <c r="H7" s="41" t="s">
+      <c r="G7" s="59">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="60">
         <v>0.43</v>
       </c>
-      <c r="J7" s="55">
+      <c r="J7" s="47">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="48">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
+    <row r="8" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="40">
         <v>12</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="50">
         <v>1.5</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="51">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="52">
         <f>[1]Sheet1!$AC$18</f>
         <v>0.25</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="53">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="55">
         <v>0.33</v>
       </c>
-      <c r="J8" s="55">
+      <c r="J8" s="56">
         <v>0.33</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="79"/>
+      <c r="B9" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="41">
         <v>20</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="8">
         <v>2.15</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="9">
         <v>0.85</v>
       </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22">
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
         <v>0.15</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="43">
         <v>0.44</v>
       </c>
-      <c r="J9" s="55">
+      <c r="J9" s="44">
         <v>0.44</v>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="61">
         <v>0.11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="79"/>
+      <c r="B10" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="41">
         <v>7</v>
       </c>
-      <c r="D10" s="19">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20">
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>0.42857142857142855</v>
       </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22">
-        <v>0</v>
-      </c>
-      <c r="H10" s="41" t="s">
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="43">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J10" s="44">
         <v>0.71</v>
       </c>
-      <c r="J10" s="55">
-        <v>0.71</v>
-      </c>
-      <c r="K10" s="41">
+      <c r="K10" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="7" t="s">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="80"/>
+      <c r="B11" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="42">
         <v>4</v>
       </c>
-      <c r="D11" s="19">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0</v>
-      </c>
-      <c r="H11" s="41" t="s">
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="58">
+        <v>0</v>
+      </c>
+      <c r="G11" s="59">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="19">
-        <v>0</v>
-      </c>
-      <c r="J11" s="22">
-        <v>0</v>
-      </c>
-      <c r="K11" s="41">
+      <c r="I11" s="60">
+        <v>0</v>
+      </c>
+      <c r="J11" s="47">
+        <v>0</v>
+      </c>
+      <c r="K11" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77" t="s">
+    <row r="12" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="40">
         <v>11</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="50">
         <v>0.63636363636363635</v>
       </c>
-      <c r="E12" s="20">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0</v>
-      </c>
-      <c r="G12" s="25">
-        <v>0</v>
-      </c>
-      <c r="H12" s="41" t="s">
+      <c r="E12" s="51">
+        <v>0</v>
+      </c>
+      <c r="F12" s="52">
+        <v>0</v>
+      </c>
+      <c r="G12" s="62">
+        <v>0</v>
+      </c>
+      <c r="H12" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-      <c r="J12" s="22">
-        <v>0</v>
-      </c>
-      <c r="K12" s="41">
+      <c r="I12" s="55">
+        <v>0</v>
+      </c>
+      <c r="J12" s="56">
+        <v>0</v>
+      </c>
+      <c r="K12" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="78"/>
-      <c r="B13" s="8" t="s">
+    <row r="13" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="82"/>
+      <c r="B13" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="41">
         <v>11</v>
       </c>
-      <c r="D13" s="19">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0</v>
-      </c>
-      <c r="G13" s="25">
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
         <v>0.27272727272727271</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="47">
-        <v>0</v>
-      </c>
-      <c r="J13" s="22">
-        <v>0</v>
-      </c>
-      <c r="K13" s="41">
+      <c r="I13" s="43">
+        <v>0</v>
+      </c>
+      <c r="J13" s="44">
+        <v>0</v>
+      </c>
+      <c r="K13" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
-      <c r="B14" s="8" t="s">
+    <row r="14" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="82"/>
+      <c r="B14" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="41">
         <v>5</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="8">
         <v>1.2</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="9">
         <v>0.6</v>
       </c>
-      <c r="F14" s="21">
-        <v>0</v>
-      </c>
-      <c r="G14" s="25">
+      <c r="F14" s="10">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
         <v>0.6</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="47">
-        <v>0</v>
-      </c>
-      <c r="J14" s="22">
-        <v>0</v>
-      </c>
-      <c r="K14" s="41">
+      <c r="I14" s="43">
+        <v>0</v>
+      </c>
+      <c r="J14" s="44">
+        <v>0</v>
+      </c>
+      <c r="K14" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="5" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="82"/>
+      <c r="B15" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="41">
         <v>4</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="8">
         <v>1.75</v>
       </c>
-      <c r="E15" s="20">
-        <v>0</v>
-      </c>
-      <c r="F15" s="21">
-        <v>0</v>
-      </c>
-      <c r="G15" s="25">
-        <v>0</v>
-      </c>
-      <c r="H15" s="41" t="s">
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="47">
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <v>0</v>
-      </c>
-      <c r="K15" s="41">
+      <c r="I15" s="43">
+        <v>0</v>
+      </c>
+      <c r="J15" s="44">
+        <v>0</v>
+      </c>
+      <c r="K15" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="5" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="79"/>
-      <c r="B16" s="10" t="s">
+    <row r="16" spans="1:11" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="83"/>
+      <c r="B16" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="42">
         <v>10</v>
       </c>
-      <c r="D16" s="23">
-        <v>0</v>
-      </c>
-      <c r="E16" s="24">
-        <v>0</v>
-      </c>
-      <c r="F16" s="26">
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="G16" s="27">
-        <v>0</v>
-      </c>
-      <c r="H16" s="42" t="s">
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="46">
         <v>1</v>
       </c>
-      <c r="J16" s="48">
-        <v>0</v>
-      </c>
-      <c r="K16" s="42">
+      <c r="J16" s="47">
+        <v>0</v>
+      </c>
+      <c r="K16" s="48">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="70"/>
-      <c r="B17" s="44" t="s">
+    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="74"/>
+      <c r="B17" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="26">
         <v>133</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="30">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="30">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="30">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="30">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="57">
+      <c r="I17" s="32">
         <v>0.25</v>
       </c>
-      <c r="J17" s="58">
+      <c r="J17" s="33">
         <v>0.25</v>
       </c>
-      <c r="K17" s="59">
+      <c r="K17" s="34">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -1956,18 +1926,18 @@
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="71"/>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="75"/>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="28"/>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="17"/>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="31"/>
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D21" s="20"/>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:K1"/>
@@ -1980,7 +1950,7 @@
     <mergeCell ref="A12:A16"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -1992,7 +1962,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2004,7 +1974,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2016,7 +1986,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2028,7 +1998,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2039,8 +2009,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="43">
+  <conditionalFormatting sqref="J4">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$I$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$I$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J10 J5">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2051,12 +2045,72 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="44">
+  <conditionalFormatting sqref="J11:J16">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$I$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$K$17/2"/>
+        <cfvo type="formula" val="$K$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7 K5">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$K$17/2"/>
+        <cfvo type="formula" val="$K$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$K$17/2"/>
+        <cfvo type="formula" val="$K$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10:K16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$K$17/2"/>
+        <cfvo type="formula" val="$I$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2379D7E6-3D1F-48FF-9DDA-DDCC4B5B422B}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{286F167A-405B-4CE6-9F58-C31BD61EB5B9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>per Program Target (target/13)</t>
-  </si>
-  <si>
     <t>Active collaborations with scaling partners</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>Full Time Equivalent (FTE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per Program Target </t>
   </si>
 </sst>
 </file>
@@ -772,33 +772,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -834,9 +807,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
@@ -894,18 +864,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -918,18 +876,60 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1372,9 +1372,9 @@
   <cols>
     <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.36328125" style="21" customWidth="1"/>
-    <col min="4" max="10" width="7.1796875" style="18" customWidth="1"/>
-    <col min="11" max="11" width="7.1796875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.36328125" style="12" customWidth="1"/>
+    <col min="4" max="10" width="7.1796875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="7.1796875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="76"/>
-      <c r="B2" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="39"/>
+      <c r="B2" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="29"/>
       <c r="D2" s="68" t="s">
         <v>1</v>
       </c>
@@ -1413,504 +1413,504 @@
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="77"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="27" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="D3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="G3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="H3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="I3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="J3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="K3" s="20" t="s">
         <v>15</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="30">
+        <v>7</v>
+      </c>
+      <c r="D4" s="46">
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="E4" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="40">
-        <v>7</v>
-      </c>
-      <c r="D4" s="50">
-        <v>2.4285714285714284</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="52">
+      <c r="F4" s="48">
         <f>[1]Sheet1!$U$18</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="G4" s="53">
-        <v>0</v>
-      </c>
-      <c r="H4" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="55">
-        <v>0</v>
-      </c>
-      <c r="J4" s="56">
-        <v>0</v>
-      </c>
-      <c r="K4" s="57">
+      <c r="G4" s="49">
+        <v>0</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="41">
+        <v>0</v>
+      </c>
+      <c r="J4" s="42">
+        <v>0</v>
+      </c>
+      <c r="K4" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="31">
         <v>23</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="50">
         <v>1</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="E5" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="52">
+        <v>0</v>
+      </c>
+      <c r="G5" s="53">
         <v>0.13043478260869565</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="43">
+      <c r="H5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="33">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="34">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="35">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="31">
         <v>4</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="50">
         <v>4.75</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="E6" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="52">
+        <v>0</v>
+      </c>
+      <c r="G6" s="53">
         <v>0.25</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="43">
-        <v>0</v>
-      </c>
-      <c r="J6" s="44">
-        <v>0</v>
-      </c>
-      <c r="K6" s="45">
+      <c r="H6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="33">
+        <v>0</v>
+      </c>
+      <c r="J6" s="34">
+        <v>0</v>
+      </c>
+      <c r="K6" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80"/>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="32">
         <v>15</v>
       </c>
-      <c r="D7" s="12">
-        <v>0</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="D7" s="54">
+        <v>0</v>
+      </c>
+      <c r="E7" s="55">
         <v>0.93333333333333335</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="56">
         <f>[1]Sheet1!$AA$18</f>
         <v>0.2</v>
       </c>
-      <c r="G7" s="59">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="60">
+      <c r="G7" s="57">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="44">
         <v>0.43</v>
       </c>
-      <c r="J7" s="47">
+      <c r="J7" s="37">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="38">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="30">
         <v>12</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="46">
         <v>1.5</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="47">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="48">
         <f>[1]Sheet1!$AC$18</f>
         <v>0.25</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="49">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H8" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="55">
+      <c r="H8" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="41">
         <v>0.33</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="42">
         <v>0.33</v>
       </c>
-      <c r="K8" s="57">
+      <c r="K8" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79"/>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="31">
         <v>20</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="50">
         <v>2.15</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="51">
         <v>0.85</v>
       </c>
-      <c r="F9" s="10">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F9" s="52">
+        <v>0</v>
+      </c>
+      <c r="G9" s="53">
         <v>0.15</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="43">
+      <c r="H9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="33">
         <v>0.44</v>
       </c>
-      <c r="J9" s="44">
+      <c r="J9" s="34">
         <v>0.44</v>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="45">
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
-      <c r="B10" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="41">
+      <c r="B10" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="31">
         <v>7</v>
       </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="D10" s="50">
+        <v>0</v>
+      </c>
+      <c r="E10" s="51">
         <v>0.42857142857142855</v>
       </c>
-      <c r="F10" s="10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="43">
+      <c r="F10" s="52">
+        <v>0</v>
+      </c>
+      <c r="G10" s="53">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="33">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="44">
+      <c r="J10" s="34">
         <v>0.71</v>
       </c>
-      <c r="K10" s="45">
+      <c r="K10" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="80"/>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="32">
         <v>4</v>
       </c>
-      <c r="D11" s="12">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="58">
-        <v>0</v>
-      </c>
-      <c r="G11" s="59">
-        <v>0</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="60">
-        <v>0</v>
-      </c>
-      <c r="J11" s="47">
-        <v>0</v>
-      </c>
-      <c r="K11" s="48">
+      <c r="D11" s="54">
+        <v>0</v>
+      </c>
+      <c r="E11" s="55">
+        <v>0</v>
+      </c>
+      <c r="F11" s="56">
+        <v>0</v>
+      </c>
+      <c r="G11" s="57">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="44">
+        <v>0</v>
+      </c>
+      <c r="J11" s="37">
+        <v>0</v>
+      </c>
+      <c r="K11" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="40">
+        <v>23</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="30">
         <v>11</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="46">
         <v>0.63636363636363635</v>
       </c>
-      <c r="E12" s="51">
-        <v>0</v>
-      </c>
-      <c r="F12" s="52">
-        <v>0</v>
-      </c>
-      <c r="G12" s="62">
-        <v>0</v>
-      </c>
-      <c r="H12" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="55">
-        <v>0</v>
-      </c>
-      <c r="J12" s="56">
-        <v>0</v>
-      </c>
-      <c r="K12" s="57">
+      <c r="E12" s="47">
+        <v>0</v>
+      </c>
+      <c r="F12" s="48">
+        <v>0</v>
+      </c>
+      <c r="G12" s="58">
+        <v>0</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="41">
+        <v>0</v>
+      </c>
+      <c r="J12" s="42">
+        <v>0</v>
+      </c>
+      <c r="K12" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="41">
+      <c r="B13" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="31">
         <v>11</v>
       </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
+      <c r="D13" s="50">
+        <v>0</v>
+      </c>
+      <c r="E13" s="51">
+        <v>0</v>
+      </c>
+      <c r="F13" s="52">
+        <v>0</v>
+      </c>
+      <c r="G13" s="59">
         <v>0.27272727272727271</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="43">
-        <v>0</v>
-      </c>
-      <c r="J13" s="44">
-        <v>0</v>
-      </c>
-      <c r="K13" s="45">
+      <c r="H13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="33">
+        <v>0</v>
+      </c>
+      <c r="J13" s="34">
+        <v>0</v>
+      </c>
+      <c r="K13" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="41">
+      <c r="B14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="31">
         <v>5</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="50">
         <v>1.2</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="51">
         <v>0.6</v>
       </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
+      <c r="F14" s="52">
+        <v>0</v>
+      </c>
+      <c r="G14" s="59">
         <v>0.6</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="43">
-        <v>0</v>
-      </c>
-      <c r="J14" s="44">
-        <v>0</v>
-      </c>
-      <c r="K14" s="45">
+      <c r="H14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="33">
+        <v>0</v>
+      </c>
+      <c r="J14" s="34">
+        <v>0</v>
+      </c>
+      <c r="K14" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="41">
+      <c r="B15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="31">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="50">
         <v>1.75</v>
       </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="43">
-        <v>0</v>
-      </c>
-      <c r="J15" s="44">
-        <v>0</v>
-      </c>
-      <c r="K15" s="45">
+      <c r="E15" s="51">
+        <v>0</v>
+      </c>
+      <c r="F15" s="52">
+        <v>0</v>
+      </c>
+      <c r="G15" s="59">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="33">
+        <v>0</v>
+      </c>
+      <c r="J15" s="34">
+        <v>0</v>
+      </c>
+      <c r="K15" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="83"/>
-      <c r="B16" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="42">
+      <c r="B16" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="32">
         <v>10</v>
       </c>
-      <c r="D16" s="12">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="D16" s="54">
+        <v>0</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0</v>
+      </c>
+      <c r="F16" s="60">
         <f>[1]Sheet1!$AS$18</f>
         <v>0.1</v>
       </c>
-      <c r="G16" s="16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="46">
+      <c r="G16" s="61">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="36">
         <v>1</v>
       </c>
-      <c r="J16" s="47">
-        <v>0</v>
-      </c>
-      <c r="K16" s="48">
+      <c r="J16" s="37">
+        <v>0</v>
+      </c>
+      <c r="K16" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="74"/>
-      <c r="B17" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="26">
+      <c r="B17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="17">
         <v>133</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="62">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="62">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="62">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="62">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="32">
+      <c r="H17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="22">
         <v>0.25</v>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="23">
         <v>0.25</v>
       </c>
-      <c r="K17" s="34">
+      <c r="K17" s="24">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -1930,11 +1930,11 @@
       <c r="A18" s="75"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
-      <c r="D19" s="17"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="20"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.35"/>
@@ -2069,10 +2069,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="K5 K7">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
         <color rgb="FFFF0000"/>
@@ -2081,10 +2081,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7 K5">
-    <cfRule type="colorScale" priority="52">
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
         <color rgb="FFFF0000"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{286F167A-405B-4CE6-9F58-C31BD61EB5B9}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D59FD05-C2FE-47AD-A058-D8BF771F5574}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
   <sheets>
     <sheet name="Reputation, Society" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Reputation, Society'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reputation, Society'!$A$1:$K$17</definedName>
@@ -658,18 +655,72 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -679,74 +730,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -757,7 +748,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -834,62 +825,40 @@
     <xf numFmtId="165" fontId="7" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -916,7 +885,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -993,6 +962,31 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1011,39 +1005,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Chart1"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="1">
-        <row r="18">
-          <cell r="U18">
-            <v>0.14285714285714285</v>
-          </cell>
-          <cell r="AA18">
-            <v>0.2</v>
-          </cell>
-          <cell r="AC18">
-            <v>0.25</v>
-          </cell>
-          <cell r="AS18">
-            <v>0.1</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1379,42 +1340,42 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5"/>
-      <c r="B1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="59"/>
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
+      <c r="A2" s="68"/>
       <c r="B2" s="25" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="29"/>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="72"/>
-      <c r="K2" s="73"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="34" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="18" t="s">
@@ -1432,7 +1393,7 @@
       <c r="H3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="80" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="19" t="s">
@@ -1443,462 +1404,458 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="70" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="76">
         <v>7</v>
       </c>
-      <c r="D4" s="46">
-        <v>2.4285714285714284</v>
-      </c>
-      <c r="E4" s="47" t="s">
+      <c r="D4" s="38">
+        <v>4.25</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="48">
-        <f>[1]Sheet1!$U$18</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="G4" s="49">
-        <v>0</v>
-      </c>
-      <c r="H4" s="40" t="s">
+      <c r="F4" s="40">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="41">
+        <v>0</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="41">
-        <v>0</v>
-      </c>
-      <c r="J4" s="42">
-        <v>0</v>
-      </c>
-      <c r="K4" s="43">
+      <c r="I4" s="81">
+        <v>0</v>
+      </c>
+      <c r="J4" s="36">
+        <v>0</v>
+      </c>
+      <c r="K4" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="77">
         <v>23</v>
       </c>
-      <c r="D5" s="50">
-        <v>1</v>
-      </c>
-      <c r="E5" s="51" t="s">
+      <c r="D5" s="42">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="52">
-        <v>0</v>
-      </c>
-      <c r="G5" s="53">
-        <v>0.13043478260869565</v>
+      <c r="F5" s="44">
+        <v>0</v>
+      </c>
+      <c r="G5" s="45">
+        <v>0.125</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="33">
+      <c r="I5" s="82">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="30">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="31">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="77">
         <v>4</v>
       </c>
-      <c r="D6" s="50">
-        <v>4.75</v>
-      </c>
-      <c r="E6" s="51" t="s">
+      <c r="D6" s="42">
+        <v>3.8</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="52">
-        <v>0</v>
-      </c>
-      <c r="G6" s="53">
-        <v>0.25</v>
+      <c r="F6" s="44">
+        <v>0</v>
+      </c>
+      <c r="G6" s="45">
+        <v>0.2</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="33">
-        <v>0</v>
-      </c>
-      <c r="J6" s="34">
-        <v>0</v>
-      </c>
-      <c r="K6" s="35">
+      <c r="I6" s="82">
+        <v>0</v>
+      </c>
+      <c r="J6" s="30">
+        <v>0</v>
+      </c>
+      <c r="K6" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="80"/>
+      <c r="A7" s="72"/>
       <c r="B7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="78">
         <v>15</v>
       </c>
-      <c r="D7" s="54">
-        <v>0</v>
-      </c>
-      <c r="E7" s="55">
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="F7" s="56">
-        <f>[1]Sheet1!$AA$18</f>
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="57">
+      <c r="D7" s="46">
+        <v>0</v>
+      </c>
+      <c r="E7" s="47">
+        <v>0.875</v>
+      </c>
+      <c r="F7" s="48">
+        <v>0.1875</v>
+      </c>
+      <c r="G7" s="49">
         <v>0</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="83">
         <v>0.43</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="32">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="33">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="70" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="76">
         <v>12</v>
       </c>
-      <c r="D8" s="46">
-        <v>1.5</v>
-      </c>
-      <c r="E8" s="47">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="F8" s="48">
-        <f>[1]Sheet1!$AC$18</f>
-        <v>0.25</v>
-      </c>
-      <c r="G8" s="49">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H8" s="40" t="s">
+      <c r="D8" s="38">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="E8" s="39">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G8" s="41">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="H8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="81">
         <v>0.33</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="36">
         <v>0.33</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="77">
         <v>20</v>
       </c>
-      <c r="D9" s="50">
-        <v>2.15</v>
-      </c>
-      <c r="E9" s="51">
-        <v>0.85</v>
-      </c>
-      <c r="F9" s="52">
-        <v>0</v>
-      </c>
-      <c r="G9" s="53">
-        <v>0.15</v>
+      <c r="D9" s="42">
+        <v>3.3076923076923075</v>
+      </c>
+      <c r="E9" s="43">
+        <v>1.3076923076923077</v>
+      </c>
+      <c r="F9" s="44">
+        <v>0</v>
+      </c>
+      <c r="G9" s="45">
+        <v>0.23076923076923078</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="82">
         <v>0.44</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="30">
         <v>0.44</v>
       </c>
-      <c r="K9" s="45">
+      <c r="K9" s="79">
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="79"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="77">
         <v>7</v>
       </c>
-      <c r="D10" s="50">
-        <v>0</v>
-      </c>
-      <c r="E10" s="51">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F10" s="52">
-        <v>0</v>
-      </c>
-      <c r="G10" s="53">
+      <c r="D10" s="42">
+        <v>0</v>
+      </c>
+      <c r="E10" s="43">
+        <v>0.375</v>
+      </c>
+      <c r="F10" s="44">
+        <v>0</v>
+      </c>
+      <c r="G10" s="45">
         <v>0</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="82">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="30">
         <v>0.71</v>
       </c>
-      <c r="K10" s="35">
+      <c r="K10" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="80"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="78">
         <v>4</v>
       </c>
-      <c r="D11" s="54">
-        <v>0</v>
-      </c>
-      <c r="E11" s="55">
-        <v>0</v>
-      </c>
-      <c r="F11" s="56">
-        <v>0</v>
-      </c>
-      <c r="G11" s="57">
+      <c r="D11" s="46">
+        <v>0</v>
+      </c>
+      <c r="E11" s="47">
+        <v>0</v>
+      </c>
+      <c r="F11" s="48">
+        <v>0</v>
+      </c>
+      <c r="G11" s="49">
         <v>0</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="44">
-        <v>0</v>
-      </c>
-      <c r="J11" s="37">
-        <v>0</v>
-      </c>
-      <c r="K11" s="38">
+      <c r="I11" s="83">
+        <v>0</v>
+      </c>
+      <c r="J11" s="32">
+        <v>0</v>
+      </c>
+      <c r="K11" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="73" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="76">
         <v>11</v>
       </c>
-      <c r="D12" s="46">
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="E12" s="47">
-        <v>0</v>
-      </c>
-      <c r="F12" s="48">
-        <v>0</v>
-      </c>
-      <c r="G12" s="58">
-        <v>0</v>
-      </c>
-      <c r="H12" s="40" t="s">
+      <c r="D12" s="38">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="40">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="41">
-        <v>0</v>
-      </c>
-      <c r="J12" s="42">
-        <v>0</v>
-      </c>
-      <c r="K12" s="43">
+      <c r="I12" s="81">
+        <v>0</v>
+      </c>
+      <c r="J12" s="36">
+        <v>0</v>
+      </c>
+      <c r="K12" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
+      <c r="A13" s="74"/>
       <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="77">
         <v>11</v>
       </c>
-      <c r="D13" s="50">
-        <v>0</v>
-      </c>
-      <c r="E13" s="51">
-        <v>0</v>
-      </c>
-      <c r="F13" s="52">
-        <v>0</v>
-      </c>
-      <c r="G13" s="59">
+      <c r="D13" s="42">
+        <v>0</v>
+      </c>
+      <c r="E13" s="43">
+        <v>0</v>
+      </c>
+      <c r="F13" s="44">
+        <v>0</v>
+      </c>
+      <c r="G13" s="51">
         <v>0.27272727272727271</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="33">
-        <v>0</v>
-      </c>
-      <c r="J13" s="34">
-        <v>0</v>
-      </c>
-      <c r="K13" s="35">
+      <c r="I13" s="82">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30">
+        <v>0</v>
+      </c>
+      <c r="K13" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="77">
         <v>5</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="42">
         <v>1.2</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="43">
         <v>0.6</v>
       </c>
-      <c r="F14" s="52">
-        <v>0</v>
-      </c>
-      <c r="G14" s="59">
+      <c r="F14" s="44">
+        <v>0</v>
+      </c>
+      <c r="G14" s="51">
         <v>0.6</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="33">
-        <v>0</v>
-      </c>
-      <c r="J14" s="34">
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+      <c r="I14" s="82">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30">
+        <v>0</v>
+      </c>
+      <c r="K14" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="77">
         <v>4</v>
       </c>
-      <c r="D15" s="50">
-        <v>1.75</v>
-      </c>
-      <c r="E15" s="51">
-        <v>0</v>
-      </c>
-      <c r="F15" s="52">
-        <v>0</v>
-      </c>
-      <c r="G15" s="59">
+      <c r="D15" s="42">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="E15" s="43">
+        <v>0</v>
+      </c>
+      <c r="F15" s="44">
+        <v>0</v>
+      </c>
+      <c r="G15" s="51">
         <v>0</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="33">
-        <v>0</v>
-      </c>
-      <c r="J15" s="34">
-        <v>0</v>
-      </c>
-      <c r="K15" s="35">
+      <c r="I15" s="82">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30">
+        <v>0</v>
+      </c>
+      <c r="K15" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="83"/>
+      <c r="A16" s="75"/>
       <c r="B16" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="78">
         <v>10</v>
       </c>
-      <c r="D16" s="54">
-        <v>0</v>
-      </c>
-      <c r="E16" s="55">
-        <v>0</v>
-      </c>
-      <c r="F16" s="60">
-        <f>[1]Sheet1!$AS$18</f>
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="61">
+      <c r="D16" s="46">
+        <v>0</v>
+      </c>
+      <c r="E16" s="47">
+        <v>0</v>
+      </c>
+      <c r="F16" s="52">
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="G16" s="53">
         <v>0</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="84">
         <v>1</v>
       </c>
-      <c r="J16" s="37">
-        <v>0</v>
-      </c>
-      <c r="K16" s="38">
+      <c r="J16" s="32">
+        <v>0</v>
+      </c>
+      <c r="K16" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="74"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="17">
         <v>133</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="54">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E17" s="54">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="54">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="54">
         <v>0.22556390977443608</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -1927,7 +1884,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A18" s="75"/>
+      <c r="A18" s="67"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="D19" s="8"/>
@@ -2069,10 +2026,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5 K7">
-    <cfRule type="colorScale" priority="52">
+  <conditionalFormatting sqref="K6">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
         <color rgb="FFFF0000"/>
@@ -2081,10 +2038,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="K7 K5">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
         <color rgb="FFFF0000"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D59FD05-C2FE-47AD-A058-D8BF771F5574}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD04372E-2DA8-4995-801E-E184DE18E38D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -240,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -732,6 +732,51 @@
     <border>
       <left/>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -786,9 +831,6 @@
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
@@ -899,78 +941,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -986,6 +956,81 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1340,534 +1385,535 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5"/>
-      <c r="B1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="59"/>
+      <c r="B1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="68"/>
-      <c r="B2" s="25" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="60" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63" t="s">
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="64"/>
-      <c r="K2" s="65"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="70"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="69"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="76">
-        <v>7</v>
-      </c>
-      <c r="D4" s="38">
+      <c r="C4" s="82">
+        <v>4</v>
+      </c>
+      <c r="D4" s="37">
         <v>4.25</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="39">
         <v>0.25</v>
       </c>
-      <c r="G4" s="41">
-        <v>0</v>
-      </c>
-      <c r="H4" s="35" t="s">
+      <c r="G4" s="40">
+        <v>0</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="81">
-        <v>0</v>
-      </c>
-      <c r="J4" s="36">
-        <v>0</v>
-      </c>
-      <c r="K4" s="37">
+      <c r="I4" s="56">
+        <v>0</v>
+      </c>
+      <c r="J4" s="35">
+        <v>0</v>
+      </c>
+      <c r="K4" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
-      <c r="B5" s="27" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="77">
-        <v>23</v>
-      </c>
-      <c r="D5" s="42">
+      <c r="C5" s="83">
+        <v>24</v>
+      </c>
+      <c r="D5" s="41">
         <v>0.95833333333333337</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="44">
-        <v>0</v>
-      </c>
-      <c r="G5" s="45">
+      <c r="F5" s="43">
+        <v>0</v>
+      </c>
+      <c r="G5" s="44">
         <v>0.125</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="82">
+      <c r="I5" s="57">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="29">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="30">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="27" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="77">
-        <v>4</v>
-      </c>
-      <c r="D6" s="42">
+      <c r="C6" s="83">
+        <v>5</v>
+      </c>
+      <c r="D6" s="41">
         <v>3.8</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="44">
-        <v>0</v>
-      </c>
-      <c r="G6" s="45">
+      <c r="F6" s="43">
+        <v>0</v>
+      </c>
+      <c r="G6" s="44">
         <v>0.2</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="82">
-        <v>0</v>
-      </c>
-      <c r="J6" s="30">
-        <v>0</v>
-      </c>
-      <c r="K6" s="31">
+      <c r="I6" s="57">
+        <v>0</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0</v>
+      </c>
+      <c r="K6" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="72"/>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="78">
-        <v>15</v>
-      </c>
-      <c r="D7" s="46">
-        <v>0</v>
-      </c>
-      <c r="E7" s="47">
+      <c r="C7" s="83">
+        <v>16</v>
+      </c>
+      <c r="D7" s="45">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46">
         <v>0.875</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="47">
         <v>0.1875</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="48">
         <v>0</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="83">
+      <c r="I7" s="58">
         <v>0.43</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="31">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="32">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="76">
-        <v>12</v>
-      </c>
-      <c r="D8" s="38">
+      <c r="C8" s="83">
+        <v>21</v>
+      </c>
+      <c r="D8" s="37">
         <v>0.8571428571428571</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="38">
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="39">
         <v>0.14285714285714285</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="40">
         <v>0.23809523809523808</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="56">
         <v>0.33</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="35">
         <v>0.33</v>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="76"/>
+      <c r="B9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="77">
-        <v>20</v>
-      </c>
-      <c r="D9" s="42">
+      <c r="C9" s="83">
+        <v>13</v>
+      </c>
+      <c r="D9" s="41">
         <v>3.3076923076923075</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="42">
         <v>1.3076923076923077</v>
       </c>
-      <c r="F9" s="44">
-        <v>0</v>
-      </c>
-      <c r="G9" s="45">
+      <c r="F9" s="43">
+        <v>0</v>
+      </c>
+      <c r="G9" s="44">
         <v>0.23076923076923078</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="82">
+      <c r="I9" s="57">
         <v>0.44</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>0.44</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="54">
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="27" t="s">
+      <c r="A10" s="76"/>
+      <c r="B10" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="77">
-        <v>7</v>
-      </c>
-      <c r="D10" s="42">
-        <v>0</v>
-      </c>
-      <c r="E10" s="43">
+      <c r="C10" s="83">
+        <v>8</v>
+      </c>
+      <c r="D10" s="41">
+        <v>0</v>
+      </c>
+      <c r="E10" s="42">
         <v>0.375</v>
       </c>
-      <c r="F10" s="44">
-        <v>0</v>
-      </c>
-      <c r="G10" s="45">
+      <c r="F10" s="43">
+        <v>0</v>
+      </c>
+      <c r="G10" s="44">
         <v>0</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="82">
+      <c r="I10" s="57">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="29">
         <v>0.71</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="72"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="77"/>
+      <c r="B11" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="78">
-        <v>4</v>
-      </c>
-      <c r="D11" s="46">
-        <v>0</v>
-      </c>
-      <c r="E11" s="47">
-        <v>0</v>
-      </c>
-      <c r="F11" s="48">
-        <v>0</v>
-      </c>
-      <c r="G11" s="49">
+      <c r="C11" s="83">
+        <v>5</v>
+      </c>
+      <c r="D11" s="45">
+        <v>0</v>
+      </c>
+      <c r="E11" s="46">
+        <v>0</v>
+      </c>
+      <c r="F11" s="47">
+        <v>0</v>
+      </c>
+      <c r="G11" s="48">
         <v>0</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="83">
-        <v>0</v>
-      </c>
-      <c r="J11" s="32">
-        <v>0</v>
-      </c>
-      <c r="K11" s="33">
+      <c r="I11" s="58">
+        <v>0</v>
+      </c>
+      <c r="J11" s="31">
+        <v>0</v>
+      </c>
+      <c r="K11" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="76">
-        <v>11</v>
-      </c>
-      <c r="D12" s="38">
+      <c r="C12" s="83">
+        <v>12</v>
+      </c>
+      <c r="D12" s="37">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="40">
-        <v>0</v>
-      </c>
-      <c r="G12" s="50">
-        <v>0</v>
-      </c>
-      <c r="H12" s="35" t="s">
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
+        <v>0</v>
+      </c>
+      <c r="G12" s="49">
+        <v>0</v>
+      </c>
+      <c r="H12" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="81">
-        <v>0</v>
-      </c>
-      <c r="J12" s="36">
-        <v>0</v>
-      </c>
-      <c r="K12" s="37">
+      <c r="I12" s="56">
+        <v>0</v>
+      </c>
+      <c r="J12" s="35">
+        <v>0</v>
+      </c>
+      <c r="K12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="27" t="s">
+      <c r="A13" s="79"/>
+      <c r="B13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="83">
         <v>11</v>
       </c>
-      <c r="D13" s="42">
-        <v>0</v>
-      </c>
-      <c r="E13" s="43">
-        <v>0</v>
-      </c>
-      <c r="F13" s="44">
-        <v>0</v>
-      </c>
-      <c r="G13" s="51">
+      <c r="D13" s="41">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42">
+        <v>0</v>
+      </c>
+      <c r="F13" s="43">
+        <v>0</v>
+      </c>
+      <c r="G13" s="50">
         <v>0.27272727272727271</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="82">
-        <v>0</v>
-      </c>
-      <c r="J13" s="30">
-        <v>0</v>
-      </c>
-      <c r="K13" s="31">
+      <c r="I13" s="57">
+        <v>0</v>
+      </c>
+      <c r="J13" s="29">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="74"/>
-      <c r="B14" s="27" t="s">
+      <c r="A14" s="79"/>
+      <c r="B14" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="83">
         <v>5</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="41">
         <v>1.2</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="42">
         <v>0.6</v>
       </c>
-      <c r="F14" s="44">
-        <v>0</v>
-      </c>
-      <c r="G14" s="51">
+      <c r="F14" s="43">
+        <v>0</v>
+      </c>
+      <c r="G14" s="50">
         <v>0.6</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="82">
-        <v>0</v>
-      </c>
-      <c r="J14" s="30">
-        <v>0</v>
-      </c>
-      <c r="K14" s="31">
+      <c r="I14" s="57">
+        <v>0</v>
+      </c>
+      <c r="J14" s="29">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="74"/>
-      <c r="B15" s="27" t="s">
+      <c r="A15" s="79"/>
+      <c r="B15" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="77">
-        <v>4</v>
-      </c>
-      <c r="D15" s="42">
+      <c r="C15" s="83">
+        <v>6</v>
+      </c>
+      <c r="D15" s="41">
         <v>1.1666666666666667</v>
       </c>
-      <c r="E15" s="43">
-        <v>0</v>
-      </c>
-      <c r="F15" s="44">
-        <v>0</v>
-      </c>
-      <c r="G15" s="51">
+      <c r="E15" s="42">
+        <v>0</v>
+      </c>
+      <c r="F15" s="43">
+        <v>0</v>
+      </c>
+      <c r="G15" s="50">
         <v>0</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="82">
-        <v>0</v>
-      </c>
-      <c r="J15" s="30">
-        <v>0</v>
-      </c>
-      <c r="K15" s="31">
+      <c r="I15" s="57">
+        <v>0</v>
+      </c>
+      <c r="J15" s="29">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="75"/>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="80"/>
+      <c r="B16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="78">
-        <v>10</v>
-      </c>
-      <c r="D16" s="46">
-        <v>0</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0</v>
-      </c>
-      <c r="F16" s="52">
+      <c r="C16" s="84">
+        <v>11</v>
+      </c>
+      <c r="D16" s="45">
+        <v>0</v>
+      </c>
+      <c r="E16" s="46">
+        <v>0</v>
+      </c>
+      <c r="F16" s="51">
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="52">
         <v>0</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="84">
+      <c r="I16" s="59">
         <v>1</v>
       </c>
-      <c r="J16" s="32">
-        <v>0</v>
-      </c>
-      <c r="K16" s="33">
+      <c r="J16" s="31">
+        <v>0</v>
+      </c>
+      <c r="K16" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="66"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="17">
-        <v>133</v>
-      </c>
-      <c r="D17" s="54">
+      <c r="C17" s="81">
+        <f>SUM(C4:C16)</f>
+        <v>141</v>
+      </c>
+      <c r="D17" s="53">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="53">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="53">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="53">
         <v>0.22556390977443608</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="21">
         <v>0.25</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="22">
         <v>0.25</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="23">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -1884,7 +1930,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A18" s="67"/>
+      <c r="A18" s="72"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="D19" s="8"/>

--- a/data/Heat map 6.xlsx
+++ b/data/Heat map 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD04372E-2DA8-4995-801E-E184DE18E38D}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{66CF1B9A-5766-47EE-9818-482376449DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{675C6A22-1C37-4B00-B778-403725DFFDC9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{76F2D5A9-3AE0-44CD-930A-817A40FC2D01}"/>
   </bookViews>
@@ -139,10 +139,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -240,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -699,45 +701,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -793,7 +756,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -843,15 +806,6 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -867,30 +821,12 @@
     <xf numFmtId="165" fontId="7" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -942,21 +878,45 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1021,16 +981,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1378,49 +1338,49 @@
   <cols>
     <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="41.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.36328125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="5.90625" style="12" customWidth="1"/>
     <col min="4" max="10" width="7.1796875" style="9" customWidth="1"/>
     <col min="11" max="11" width="7.1796875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5"/>
-      <c r="B1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="63"/>
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="73"/>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="65" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="69"/>
-      <c r="K2" s="70"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="26" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="17" t="s">
@@ -1438,7 +1398,7 @@
       <c r="H3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="17" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="18" t="s">
@@ -1449,471 +1409,471 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="82">
+      <c r="C4" s="45">
         <v>4</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="28">
         <v>4.25</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="30">
         <v>0.25</v>
       </c>
-      <c r="G4" s="40">
-        <v>0</v>
-      </c>
-      <c r="H4" s="34" t="s">
+      <c r="G4" s="31">
+        <v>0</v>
+      </c>
+      <c r="H4" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="56">
-        <v>0</v>
-      </c>
-      <c r="J4" s="35">
-        <v>0</v>
-      </c>
-      <c r="K4" s="36">
+      <c r="I4" s="80">
+        <v>0</v>
+      </c>
+      <c r="J4" s="49">
+        <v>0</v>
+      </c>
+      <c r="K4" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76"/>
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5" s="46">
         <v>24</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="32">
         <v>0.95833333333333337</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="43">
-        <v>0</v>
-      </c>
-      <c r="G5" s="44">
+      <c r="F5" s="34">
+        <v>0</v>
+      </c>
+      <c r="G5" s="35">
         <v>0.125</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="81">
         <v>0.28999999999999998</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="51">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="52">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76"/>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="75"/>
+      <c r="B6" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="46">
         <v>5</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="32">
         <v>3.8</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="43">
-        <v>0</v>
-      </c>
-      <c r="G6" s="44">
+      <c r="F6" s="34">
+        <v>0</v>
+      </c>
+      <c r="G6" s="35">
         <v>0.2</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="57">
-        <v>0</v>
-      </c>
-      <c r="J6" s="29">
-        <v>0</v>
-      </c>
-      <c r="K6" s="30">
+      <c r="I6" s="81">
+        <v>0</v>
+      </c>
+      <c r="J6" s="51">
+        <v>0</v>
+      </c>
+      <c r="K6" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="77"/>
-      <c r="B7" s="27" t="s">
+      <c r="A7" s="76"/>
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="83">
+      <c r="C7" s="47">
         <v>16</v>
       </c>
-      <c r="D7" s="45">
-        <v>0</v>
-      </c>
-      <c r="E7" s="46">
+      <c r="D7" s="36">
+        <v>0</v>
+      </c>
+      <c r="E7" s="37">
         <v>0.875</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="38">
         <v>0.1875</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="39">
         <v>0</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="82">
         <v>0.43</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="53">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="54">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="45">
         <v>21</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="28">
         <v>0.8571428571428571</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="29">
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="30">
         <v>0.14285714285714285</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="31">
         <v>0.23809523809523808</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="80">
         <v>0.33</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="49">
         <v>0.33</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="26" t="s">
+      <c r="A9" s="75"/>
+      <c r="B9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="46">
         <v>13</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="32">
         <v>3.3076923076923075</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="33">
         <v>1.3076923076923077</v>
       </c>
-      <c r="F9" s="43">
-        <v>0</v>
-      </c>
-      <c r="G9" s="44">
+      <c r="F9" s="34">
+        <v>0</v>
+      </c>
+      <c r="G9" s="35">
         <v>0.23076923076923078</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="81">
         <v>0.44</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="51">
         <v>0.44</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="55">
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
-      <c r="B10" s="26" t="s">
+      <c r="A10" s="75"/>
+      <c r="B10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="83">
+      <c r="C10" s="46">
         <v>8</v>
       </c>
-      <c r="D10" s="41">
-        <v>0</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="D10" s="32">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
         <v>0.375</v>
       </c>
-      <c r="F10" s="43">
-        <v>0</v>
-      </c>
-      <c r="G10" s="44">
+      <c r="F10" s="34">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35">
         <v>0</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="57">
+      <c r="I10" s="81">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="51">
         <v>0.71</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="77"/>
-      <c r="B11" s="27" t="s">
+      <c r="A11" s="76"/>
+      <c r="B11" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="47">
         <v>5</v>
       </c>
-      <c r="D11" s="45">
-        <v>0</v>
-      </c>
-      <c r="E11" s="46">
-        <v>0</v>
-      </c>
-      <c r="F11" s="47">
-        <v>0</v>
-      </c>
-      <c r="G11" s="48">
+      <c r="D11" s="36">
+        <v>0</v>
+      </c>
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="38">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39">
         <v>0</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="58">
-        <v>0</v>
-      </c>
-      <c r="J11" s="31">
-        <v>0</v>
-      </c>
-      <c r="K11" s="32">
+      <c r="I11" s="82">
+        <v>0</v>
+      </c>
+      <c r="J11" s="53">
+        <v>0</v>
+      </c>
+      <c r="K11" s="54">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="45">
         <v>12</v>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="28">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E12" s="38">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>0</v>
-      </c>
-      <c r="G12" s="49">
-        <v>0</v>
-      </c>
-      <c r="H12" s="34" t="s">
+      <c r="E12" s="29">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
+        <v>0</v>
+      </c>
+      <c r="G12" s="40">
+        <v>0</v>
+      </c>
+      <c r="H12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="56">
-        <v>0</v>
-      </c>
-      <c r="J12" s="35">
-        <v>0</v>
-      </c>
-      <c r="K12" s="36">
+      <c r="I12" s="80">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49">
+        <v>0</v>
+      </c>
+      <c r="K12" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="79"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="78"/>
+      <c r="B13" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="83">
+      <c r="C13" s="46">
         <v>11</v>
       </c>
-      <c r="D13" s="41">
-        <v>0</v>
-      </c>
-      <c r="E13" s="42">
-        <v>0</v>
-      </c>
-      <c r="F13" s="43">
-        <v>0</v>
-      </c>
-      <c r="G13" s="50">
+      <c r="D13" s="32">
+        <v>0</v>
+      </c>
+      <c r="E13" s="33">
+        <v>0</v>
+      </c>
+      <c r="F13" s="34">
+        <v>0</v>
+      </c>
+      <c r="G13" s="41">
         <v>0.27272727272727271</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="57">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29">
-        <v>0</v>
-      </c>
-      <c r="K13" s="30">
+      <c r="I13" s="81">
+        <v>0</v>
+      </c>
+      <c r="J13" s="51">
+        <v>0</v>
+      </c>
+      <c r="K13" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="79"/>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="78"/>
+      <c r="B14" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="83">
+      <c r="C14" s="46">
         <v>5</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="32">
         <v>1.2</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="33">
         <v>0.6</v>
       </c>
-      <c r="F14" s="43">
-        <v>0</v>
-      </c>
-      <c r="G14" s="50">
+      <c r="F14" s="34">
+        <v>0</v>
+      </c>
+      <c r="G14" s="41">
         <v>0.6</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="57">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29">
-        <v>0</v>
-      </c>
-      <c r="K14" s="30">
+      <c r="I14" s="81">
+        <v>0</v>
+      </c>
+      <c r="J14" s="51">
+        <v>0</v>
+      </c>
+      <c r="K14" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="4" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="79"/>
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="78"/>
+      <c r="B15" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="83">
+      <c r="C15" s="46">
         <v>6</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="32">
         <v>1.1666666666666667</v>
       </c>
-      <c r="E15" s="42">
-        <v>0</v>
-      </c>
-      <c r="F15" s="43">
-        <v>0</v>
-      </c>
-      <c r="G15" s="50">
+      <c r="E15" s="33">
+        <v>0</v>
+      </c>
+      <c r="F15" s="34">
+        <v>0</v>
+      </c>
+      <c r="G15" s="41">
         <v>0</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="57">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29">
-        <v>0</v>
-      </c>
-      <c r="K15" s="30">
+      <c r="I15" s="81">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51">
+        <v>0</v>
+      </c>
+      <c r="K15" s="52">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="4" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="80"/>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="84">
+      <c r="C16" s="47">
         <v>11</v>
       </c>
-      <c r="D16" s="45">
-        <v>0</v>
-      </c>
-      <c r="E16" s="46">
-        <v>0</v>
-      </c>
-      <c r="F16" s="51">
+      <c r="D16" s="36">
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42">
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="43">
         <v>0</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="59">
+      <c r="I16" s="83">
         <v>1</v>
       </c>
-      <c r="J16" s="31">
-        <v>0</v>
-      </c>
-      <c r="K16" s="32">
+      <c r="J16" s="53">
+        <v>0</v>
+      </c>
+      <c r="K16" s="54">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="71"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="81">
+      <c r="C17" s="48">
         <f>SUM(C4:C16)</f>
         <v>141</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="44">
         <v>0.22556390977443608</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="44">
         <v>0.18796992481203006</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="44">
         <v>0.22556390977443608</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="44">
         <v>0.22556390977443608</v>
       </c>
       <c r="H17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="56">
         <v>0.25</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="57">
         <v>0.25</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="58">
         <v>0.25</v>
       </c>
       <c r="L17" s="2"/>
@@ -1930,7 +1890,7 @@
       <c r="W17" s="2"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A18" s="72"/>
+      <c r="A18" s="71"/>
     </row>
     <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="D19" s="8"/>
